--- a/data/fmsForecastOutput/File1/RPT_RPT7294033893830TY_fmsForecastOutput.xlsx
+++ b/data/fmsForecastOutput/File1/RPT_RPT7294033893830TY_fmsForecastOutput.xlsx
@@ -1878,31 +1878,31 @@
         <v>458.4688261402947</v>
       </c>
       <c r="D8" s="149" t="n">
-        <v>486.8618228693556</v>
+        <v>486.8618228693555</v>
       </c>
       <c r="E8" s="149" t="n">
-        <v>519.8945746310864</v>
+        <v>519.8945746310862</v>
       </c>
       <c r="F8" s="149" t="n">
         <v>547.6158175572276</v>
       </c>
       <c r="G8" s="150" t="n">
-        <v>577.7628316979046</v>
+        <v>577.7628316979044</v>
       </c>
       <c r="H8" s="148" t="n">
-        <v>454.5851368213867</v>
+        <v>454.5851368213866</v>
       </c>
       <c r="I8" s="149" t="n">
-        <v>483.7951970966897</v>
+        <v>483.7951970966895</v>
       </c>
       <c r="J8" s="149" t="n">
-        <v>517.6704726029917</v>
+        <v>517.6704726029916</v>
       </c>
       <c r="K8" s="149" t="n">
         <v>546.3733946600989</v>
       </c>
       <c r="L8" s="150" t="n">
-        <v>577.6244182146326</v>
+        <v>577.6244182146323</v>
       </c>
       <c r="M8" s="151" t="n">
         <v>52896290.20228141</v>
@@ -1917,7 +1917,7 @@
         <v>77801415.02163078</v>
       </c>
       <c r="Q8" s="153" t="n">
-        <v>90267406.43371172</v>
+        <v>90267406.43371171</v>
       </c>
       <c r="S8" s="21" t="inlineStr">
         <is>
@@ -1925,34 +1925,34 @@
         </is>
       </c>
       <c r="T8" s="148" t="n">
-        <v>562.5903825870338</v>
+        <v>562.5903825870337</v>
       </c>
       <c r="U8" s="149" t="n">
-        <v>597.4316323772796</v>
+        <v>597.4316323772794</v>
       </c>
       <c r="V8" s="149" t="n">
-        <v>637.9663588231032</v>
+        <v>637.9663588231031</v>
       </c>
       <c r="W8" s="149" t="n">
         <v>671.9832947070566</v>
       </c>
       <c r="X8" s="150" t="n">
-        <v>708.976911834844</v>
+        <v>708.9769118348438</v>
       </c>
       <c r="Y8" s="148" t="n">
         <v>557.87813995581</v>
       </c>
       <c r="Z8" s="149" t="n">
-        <v>593.7108585498023</v>
+        <v>593.7108585498022</v>
       </c>
       <c r="AA8" s="149" t="n">
-        <v>635.2678908504294</v>
+        <v>635.2678908504292</v>
       </c>
       <c r="AB8" s="149" t="n">
         <v>670.475916830582</v>
       </c>
       <c r="AC8" s="150" t="n">
-        <v>708.8089846069307</v>
+        <v>708.8089846069306</v>
       </c>
       <c r="AD8" s="151" t="n">
         <v>52896290.20228141</v>
@@ -1967,7 +1967,7 @@
         <v>77801415.02163078</v>
       </c>
       <c r="AH8" s="153" t="n">
-        <v>90267406.43371172</v>
+        <v>90267406.43371171</v>
       </c>
       <c r="AQ8" s="28" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>1017.459089724621</v>
       </c>
       <c r="D9" s="156" t="n">
-        <v>1070.108217761866</v>
+        <v>1070.108217761865</v>
       </c>
       <c r="E9" s="156" t="n">
         <v>1136.405381929706</v>
@@ -2040,10 +2040,10 @@
         <v>1008.392970668675</v>
       </c>
       <c r="I9" s="156" t="n">
-        <v>1062.512190779732</v>
+        <v>1062.512190779731</v>
       </c>
       <c r="J9" s="156" t="n">
-        <v>1130.486399462452</v>
+        <v>1130.486399462451</v>
       </c>
       <c r="K9" s="156" t="n">
         <v>1182.363996795883</v>
@@ -2055,10 +2055,10 @@
         <v>26185379.03705674</v>
       </c>
       <c r="N9" s="159" t="n">
-        <v>28339830.28143753</v>
+        <v>28339830.28143752</v>
       </c>
       <c r="O9" s="159" t="n">
-        <v>31393998.41144255</v>
+        <v>31393998.41144254</v>
       </c>
       <c r="P9" s="159" t="n">
         <v>35040424.50268856</v>
@@ -2075,10 +2075,10 @@
         <v>1029.255918687301</v>
       </c>
       <c r="U9" s="156" t="n">
-        <v>1082.515481841557</v>
+        <v>1082.515481841556</v>
       </c>
       <c r="V9" s="156" t="n">
-        <v>1149.581321933861</v>
+        <v>1149.58132193386</v>
       </c>
       <c r="W9" s="156" t="n">
         <v>1199.871447407734</v>
@@ -2093,7 +2093,7 @@
         <v>1074.769372405458</v>
       </c>
       <c r="AA9" s="156" t="n">
-        <v>1143.545299376819</v>
+        <v>1143.545299376818</v>
       </c>
       <c r="AB9" s="156" t="n">
         <v>1196.042021740731</v>
@@ -2105,10 +2105,10 @@
         <v>26185379.03705674</v>
       </c>
       <c r="AE9" s="159" t="n">
-        <v>28339830.28143753</v>
+        <v>28339830.28143752</v>
       </c>
       <c r="AF9" s="159" t="n">
-        <v>31393998.41144255</v>
+        <v>31393998.41144254</v>
       </c>
       <c r="AG9" s="159" t="n">
         <v>35040424.50268856</v>
@@ -2170,40 +2170,40 @@
         </is>
       </c>
       <c r="C10" s="161" t="n">
-        <v>560.4176239635417</v>
+        <v>560.4176239635416</v>
       </c>
       <c r="D10" s="162" t="n">
-        <v>589.8242254012563</v>
+        <v>589.8242254012561</v>
       </c>
       <c r="E10" s="162" t="n">
-        <v>626.7373682157119</v>
+        <v>626.7373682157116</v>
       </c>
       <c r="F10" s="162" t="n">
         <v>657.5287470822957</v>
       </c>
       <c r="G10" s="163" t="n">
-        <v>691.1959923103492</v>
+        <v>691.195992310349</v>
       </c>
       <c r="H10" s="161" t="n">
-        <v>555.6253841739881</v>
+        <v>555.625384173988</v>
       </c>
       <c r="I10" s="162" t="n">
         <v>586.0257503979303</v>
       </c>
       <c r="J10" s="162" t="n">
-        <v>623.9550467796744</v>
+        <v>623.9550467796741</v>
       </c>
       <c r="K10" s="162" t="n">
         <v>655.9353394508906</v>
       </c>
       <c r="L10" s="163" t="n">
-        <v>690.9314916279108</v>
+        <v>690.9314916279105</v>
       </c>
       <c r="M10" s="164" t="n">
         <v>79081669.23933813</v>
       </c>
       <c r="N10" s="165" t="n">
-        <v>88484162.99557489</v>
+        <v>88484162.99557488</v>
       </c>
       <c r="O10" s="165" t="n">
         <v>99906650.50108618</v>
@@ -2212,7 +2212,7 @@
         <v>112841839.5243193</v>
       </c>
       <c r="Q10" s="166" t="n">
-        <v>130287315.7461006</v>
+        <v>130287315.7461005</v>
       </c>
       <c r="S10" s="42" t="inlineStr">
         <is>
@@ -2223,7 +2223,7 @@
         <v>661.9717179153973</v>
       </c>
       <c r="U10" s="162" t="n">
-        <v>697.5435349434621</v>
+        <v>697.543534943462</v>
       </c>
       <c r="V10" s="162" t="n">
         <v>741.6901225440172</v>
@@ -2232,13 +2232,13 @@
         <v>778.3147219607389</v>
       </c>
       <c r="X10" s="163" t="n">
-        <v>818.3347258476837</v>
+        <v>818.3347258476834</v>
       </c>
       <c r="Y10" s="161" t="n">
         <v>656.3415389942157</v>
       </c>
       <c r="Z10" s="162" t="n">
-        <v>693.0656179432398</v>
+        <v>693.0656179432395</v>
       </c>
       <c r="AA10" s="162" t="n">
         <v>738.3992976419279</v>
@@ -2247,13 +2247,13 @@
         <v>776.420033560413</v>
       </c>
       <c r="AC10" s="163" t="n">
-        <v>818.0019644874264</v>
+        <v>818.0019644874261</v>
       </c>
       <c r="AD10" s="164" t="n">
         <v>79081669.23933813</v>
       </c>
       <c r="AE10" s="165" t="n">
-        <v>88484162.99557489</v>
+        <v>88484162.99557488</v>
       </c>
       <c r="AF10" s="165" t="n">
         <v>99906650.50108618</v>
@@ -2262,7 +2262,7 @@
         <v>112841839.5243193</v>
       </c>
       <c r="AH10" s="166" t="n">
-        <v>130287315.7461006</v>
+        <v>130287315.7461005</v>
       </c>
       <c r="AJ10" s="39" t="n"/>
       <c r="AQ10" s="40" t="inlineStr">
@@ -2357,7 +2357,7 @@
         <v>12953290.64971427</v>
       </c>
       <c r="P11" s="159" t="n">
-        <v>14745983.66859445</v>
+        <v>14745983.66859446</v>
       </c>
       <c r="Q11" s="160" t="n">
         <v>17074220.62643371</v>
@@ -2368,7 +2368,7 @@
         </is>
       </c>
       <c r="T11" s="155" t="n">
-        <v>1435.183019264909</v>
+        <v>1435.18301926491</v>
       </c>
       <c r="U11" s="156" t="n">
         <v>1497.312785498023</v>
@@ -2380,10 +2380,10 @@
         <v>1616.525503537854</v>
       </c>
       <c r="X11" s="157" t="n">
-        <v>1658.383263281288</v>
+        <v>1658.383263281289</v>
       </c>
       <c r="Y11" s="155" t="n">
-        <v>1428.530249017573</v>
+        <v>1428.530249017574</v>
       </c>
       <c r="Z11" s="156" t="n">
         <v>1493.206344253717</v>
@@ -2395,7 +2395,7 @@
         <v>1616.525503537854</v>
       </c>
       <c r="AC11" s="157" t="n">
-        <v>1658.383263281288</v>
+        <v>1658.383263281289</v>
       </c>
       <c r="AD11" s="158" t="n">
         <v>10125003.71617656</v>
@@ -2407,7 +2407,7 @@
         <v>12953290.64971427</v>
       </c>
       <c r="AG11" s="159" t="n">
-        <v>14745983.66859445</v>
+        <v>14745983.66859446</v>
       </c>
       <c r="AH11" s="160" t="n">
         <v>17074220.62643371</v>
@@ -2464,46 +2464,46 @@
         <v>595.9154982200191</v>
       </c>
       <c r="D12" s="162" t="n">
-        <v>627.019283128718</v>
+        <v>627.0192831287179</v>
       </c>
       <c r="E12" s="162" t="n">
-        <v>666.0405094103264</v>
+        <v>666.0405094103262</v>
       </c>
       <c r="F12" s="162" t="n">
         <v>698.2873477899968</v>
       </c>
       <c r="G12" s="163" t="n">
-        <v>733.0545261349389</v>
+        <v>733.0545261349388</v>
       </c>
       <c r="H12" s="161" t="n">
         <v>590.9638639981431</v>
       </c>
       <c r="I12" s="162" t="n">
-        <v>623.1222483816329</v>
+        <v>623.1222483816326</v>
       </c>
       <c r="J12" s="162" t="n">
-        <v>663.2256927276853</v>
+        <v>663.2256927276852</v>
       </c>
       <c r="K12" s="162" t="n">
-        <v>696.6977376623872</v>
+        <v>696.6977376623873</v>
       </c>
       <c r="L12" s="163" t="n">
-        <v>732.7914840204845</v>
+        <v>732.7914840204843</v>
       </c>
       <c r="M12" s="164" t="n">
         <v>89206672.9555147</v>
       </c>
       <c r="N12" s="165" t="n">
-        <v>99861986.52537383</v>
+        <v>99861986.52537382</v>
       </c>
       <c r="O12" s="165" t="n">
-        <v>112859941.1508005</v>
+        <v>112859941.1508004</v>
       </c>
       <c r="P12" s="165" t="n">
         <v>127587823.1929138</v>
       </c>
       <c r="Q12" s="166" t="n">
-        <v>147361536.3725343</v>
+        <v>147361536.3725342</v>
       </c>
       <c r="S12" s="42" t="inlineStr">
         <is>
@@ -2511,49 +2511,49 @@
         </is>
       </c>
       <c r="T12" s="161" t="n">
-        <v>705.0870243725237</v>
+        <v>705.0870243725236</v>
       </c>
       <c r="U12" s="162" t="n">
-        <v>742.7448212954637</v>
+        <v>742.7448212954636</v>
       </c>
       <c r="V12" s="162" t="n">
-        <v>789.4881941159165</v>
+        <v>789.4881941159164</v>
       </c>
       <c r="W12" s="162" t="n">
-        <v>827.931627589575</v>
+        <v>827.9316275895749</v>
       </c>
       <c r="X12" s="163" t="n">
-        <v>869.3588179187898</v>
+        <v>869.3588179187893</v>
       </c>
       <c r="Y12" s="161" t="n">
-        <v>699.2417266850057</v>
+        <v>699.2417266850056</v>
       </c>
       <c r="Z12" s="162" t="n">
-        <v>738.1305502105575</v>
+        <v>738.1305502105574</v>
       </c>
       <c r="AA12" s="162" t="n">
-        <v>786.1463333456469</v>
+        <v>786.1463333456468</v>
       </c>
       <c r="AB12" s="162" t="n">
-        <v>826.0351847059256</v>
+        <v>826.0351847059255</v>
       </c>
       <c r="AC12" s="163" t="n">
-        <v>869.0267722811531</v>
+        <v>869.0267722811525</v>
       </c>
       <c r="AD12" s="164" t="n">
         <v>89206672.9555147</v>
       </c>
       <c r="AE12" s="165" t="n">
-        <v>99861986.52537383</v>
+        <v>99861986.52537382</v>
       </c>
       <c r="AF12" s="165" t="n">
-        <v>112859941.1508005</v>
+        <v>112859941.1508004</v>
       </c>
       <c r="AG12" s="165" t="n">
         <v>127587823.1929138</v>
       </c>
       <c r="AH12" s="166" t="n">
-        <v>147361536.3725343</v>
+        <v>147361536.3725342</v>
       </c>
       <c r="AQ12" s="40" t="inlineStr">
         <is>
@@ -2603,49 +2603,49 @@
         </is>
       </c>
       <c r="C13" s="155" t="n">
-        <v>6840.782953736923</v>
+        <v>6840.782953736918</v>
       </c>
       <c r="D13" s="156" t="n">
-        <v>6946.161324646021</v>
+        <v>6946.161324646018</v>
       </c>
       <c r="E13" s="156" t="n">
-        <v>7311.858462984306</v>
+        <v>7311.858462984304</v>
       </c>
       <c r="F13" s="156" t="n">
-        <v>7413.664273727154</v>
+        <v>7413.664273727151</v>
       </c>
       <c r="G13" s="157" t="n">
-        <v>7694.869845154931</v>
+        <v>7694.869845154927</v>
       </c>
       <c r="H13" s="155" t="n">
-        <v>6834.400158619271</v>
+        <v>6834.400158619267</v>
       </c>
       <c r="I13" s="156" t="n">
-        <v>6940.330663205697</v>
+        <v>6940.330663205695</v>
       </c>
       <c r="J13" s="156" t="n">
-        <v>7306.244288533099</v>
+        <v>7306.244288533098</v>
       </c>
       <c r="K13" s="156" t="n">
-        <v>7408.630879889043</v>
+        <v>7408.63087988904</v>
       </c>
       <c r="L13" s="157" t="n">
-        <v>7690.260878346114</v>
+        <v>7690.26087834611</v>
       </c>
       <c r="M13" s="158" t="n">
-        <v>63511781.90692843</v>
+        <v>63511781.90692839</v>
       </c>
       <c r="N13" s="159" t="n">
-        <v>72728806.67317753</v>
+        <v>72728806.6731775</v>
       </c>
       <c r="O13" s="159" t="n">
-        <v>85466913.86564565</v>
+        <v>85466913.86564563</v>
       </c>
       <c r="P13" s="159" t="n">
-        <v>99312599.84753951</v>
+        <v>99312599.84753947</v>
       </c>
       <c r="Q13" s="160" t="n">
-        <v>118406970.142038</v>
+        <v>118406970.1420379</v>
       </c>
       <c r="S13" s="32" t="inlineStr">
         <is>
@@ -2653,49 +2653,49 @@
         </is>
       </c>
       <c r="T13" s="155" t="n">
-        <v>4386.768000065688</v>
+        <v>4386.768000065686</v>
       </c>
       <c r="U13" s="156" t="n">
-        <v>4454.343666261992</v>
+        <v>4454.343666261991</v>
       </c>
       <c r="V13" s="156" t="n">
         <v>4688.853153703285</v>
       </c>
       <c r="W13" s="156" t="n">
-        <v>4754.137855148681</v>
+        <v>4754.13785514868</v>
       </c>
       <c r="X13" s="157" t="n">
-        <v>4934.465693427146</v>
+        <v>4934.465693427144</v>
       </c>
       <c r="Y13" s="155" t="n">
-        <v>4383.722179384189</v>
+        <v>4383.722179384186</v>
       </c>
       <c r="Z13" s="156" t="n">
-        <v>4451.561386243868</v>
+        <v>4451.561386243866</v>
       </c>
       <c r="AA13" s="156" t="n">
-        <v>4686.174226246619</v>
+        <v>4686.174226246618</v>
       </c>
       <c r="AB13" s="156" t="n">
-        <v>4751.736114669531</v>
+        <v>4751.736114669528</v>
       </c>
       <c r="AC13" s="157" t="n">
-        <v>4932.266518114321</v>
+        <v>4932.26651811432</v>
       </c>
       <c r="AD13" s="158" t="n">
-        <v>63511781.90692843</v>
+        <v>63511781.90692839</v>
       </c>
       <c r="AE13" s="159" t="n">
-        <v>72728806.67317753</v>
+        <v>72728806.6731775</v>
       </c>
       <c r="AF13" s="159" t="n">
-        <v>85466913.86564565</v>
+        <v>85466913.86564563</v>
       </c>
       <c r="AG13" s="159" t="n">
-        <v>99312599.84753951</v>
+        <v>99312599.84753947</v>
       </c>
       <c r="AH13" s="160" t="n">
-        <v>118406970.142038</v>
+        <v>118406970.1420379</v>
       </c>
       <c r="AJ13" s="39" t="n"/>
       <c r="AQ13" s="49" t="inlineStr">
@@ -2746,13 +2746,13 @@
         </is>
       </c>
       <c r="C14" s="167" t="n">
-        <v>960.6073977513222</v>
+        <v>960.607397751322</v>
       </c>
       <c r="D14" s="168" t="n">
         <v>1016.825145909004</v>
       </c>
       <c r="E14" s="168" t="n">
-        <v>1094.894467951161</v>
+        <v>1094.89446795116</v>
       </c>
       <c r="F14" s="168" t="n">
         <v>1156.998537716707</v>
@@ -2761,13 +2761,13 @@
         <v>1228.068700983788</v>
       </c>
       <c r="H14" s="167" t="n">
-        <v>953.0363487623126</v>
+        <v>953.0363487623123</v>
       </c>
       <c r="I14" s="168" t="n">
-        <v>1010.840888361949</v>
+        <v>1010.840888361948</v>
       </c>
       <c r="J14" s="168" t="n">
-        <v>1090.510785940966</v>
+        <v>1090.510785940965</v>
       </c>
       <c r="K14" s="168" t="n">
         <v>1154.490764232933</v>
@@ -2779,7 +2779,7 @@
         <v>152718454.8624431</v>
       </c>
       <c r="N14" s="171" t="n">
-        <v>172590793.1985514</v>
+        <v>172590793.1985513</v>
       </c>
       <c r="O14" s="171" t="n">
         <v>198326855.0164461</v>
@@ -2799,7 +2799,7 @@
         <v>1083.134913962896</v>
       </c>
       <c r="U14" s="168" t="n">
-        <v>1144.671760159198</v>
+        <v>1144.671760159197</v>
       </c>
       <c r="V14" s="168" t="n">
         <v>1230.460676113902</v>
@@ -2811,7 +2811,7 @@
         <v>1373.467127139631</v>
       </c>
       <c r="Y14" s="167" t="n">
-        <v>1074.994577015421</v>
+        <v>1074.99457701542</v>
       </c>
       <c r="Z14" s="168" t="n">
         <v>1138.249724334147</v>
@@ -2823,13 +2823,13 @@
         <v>1293.924078959097</v>
       </c>
       <c r="AC14" s="169" t="n">
-        <v>1372.931685009227</v>
+        <v>1372.931685009226</v>
       </c>
       <c r="AD14" s="170" t="n">
         <v>152718454.8624431</v>
       </c>
       <c r="AE14" s="171" t="n">
-        <v>172590793.1985514</v>
+        <v>172590793.1985513</v>
       </c>
       <c r="AF14" s="171" t="n">
         <v>198326855.0164461</v>
@@ -3158,7 +3158,7 @@
         <v>123534.7071570992</v>
       </c>
       <c r="E19" s="75" t="n">
-        <v>131781.8177623025</v>
+        <v>131781.8177623026</v>
       </c>
       <c r="F19" s="75" t="n">
         <v>142072.9871695138</v>
@@ -3202,7 +3202,7 @@
         </is>
       </c>
       <c r="T19" s="74" t="n">
-        <v>94022.74165982254</v>
+        <v>94022.74165982255</v>
       </c>
       <c r="U19" s="75" t="n">
         <v>100671.4901834258</v>
@@ -3232,7 +3232,7 @@
         <v>30.16412813999912</v>
       </c>
       <c r="AD19" s="74" t="n">
-        <v>94816.92580116398</v>
+        <v>94816.92580116399</v>
       </c>
       <c r="AE19" s="75" t="n">
         <v>101302.3963567819</v>
@@ -3325,7 +3325,7 @@
         <v>26672.47541003757</v>
       </c>
       <c r="O20" s="80" t="n">
-        <v>27770.34595583852</v>
+        <v>27770.34595583853</v>
       </c>
       <c r="P20" s="80" t="n">
         <v>29635.90281643001</v>
@@ -3345,7 +3345,7 @@
         <v>26179.60736526955</v>
       </c>
       <c r="V20" s="80" t="n">
-        <v>27309.07140925933</v>
+        <v>27309.07140925934</v>
       </c>
       <c r="W20" s="80" t="n">
         <v>29203.48223836126</v>
@@ -3375,7 +3375,7 @@
         <v>26368.28980156898</v>
       </c>
       <c r="AF20" s="80" t="n">
-        <v>27453.21801292077</v>
+        <v>27453.21801292078</v>
       </c>
       <c r="AG20" s="80" t="n">
         <v>29296.98444180949</v>
@@ -3415,7 +3415,7 @@
         <v>150017.8513952683</v>
       </c>
       <c r="E21" s="86" t="n">
-        <v>159407.5215038081</v>
+        <v>159407.5215038082</v>
       </c>
       <c r="F21" s="86" t="n">
         <v>171615.0662994452</v>
@@ -3445,7 +3445,7 @@
         <v>150990.2302680237</v>
       </c>
       <c r="O21" s="86" t="n">
-        <v>160118.3466929539</v>
+        <v>160118.346692954</v>
       </c>
       <c r="P21" s="86" t="n">
         <v>172031.9561052827</v>
@@ -3742,7 +3742,7 @@
         <v>170168.2283848731</v>
       </c>
       <c r="P23" s="86" t="n">
-        <v>183132.2484568503</v>
+        <v>183132.2484568502</v>
       </c>
       <c r="Q23" s="87" t="n">
         <v>201096.1366035948</v>
@@ -3762,16 +3762,16 @@
         <v>142953.2980884953</v>
       </c>
       <c r="W23" s="86" t="n">
-        <v>154104.2991247606</v>
+        <v>154104.2991247607</v>
       </c>
       <c r="X23" s="87" t="n">
-        <v>169506.0006699097</v>
+        <v>169506.0006699098</v>
       </c>
       <c r="Y23" s="85" t="n">
         <v>1057.63037909861</v>
       </c>
       <c r="Z23" s="86" t="n">
-        <v>840.4860188768221</v>
+        <v>840.486018876822</v>
       </c>
       <c r="AA23" s="86" t="n">
         <v>607.685870427589</v>
@@ -3795,7 +3795,7 @@
         <v>154458.0976152196</v>
       </c>
       <c r="AH23" s="87" t="n">
-        <v>169570.7670613155</v>
+        <v>169570.7670613156</v>
       </c>
       <c r="AR23" s="90" t="inlineStr">
         <is>
@@ -3948,7 +3948,7 @@
         <v>169734.9774373071</v>
       </c>
       <c r="E25" s="92" t="n">
-        <v>181137.8729381732</v>
+        <v>181137.8729381733</v>
       </c>
       <c r="F25" s="92" t="n">
         <v>196111.2444344421</v>
@@ -3966,7 +3966,7 @@
         <v>728.145787461238</v>
       </c>
       <c r="K25" s="92" t="n">
-        <v>425.9909164274645</v>
+        <v>425.9909164274644</v>
       </c>
       <c r="L25" s="93" t="n">
         <v>81.38165439183648</v>
@@ -3978,7 +3978,7 @@
         <v>170739.8218509265</v>
       </c>
       <c r="O25" s="92" t="n">
-        <v>181866.0187256345</v>
+        <v>181866.0187256346</v>
       </c>
       <c r="P25" s="92" t="n">
         <v>196537.2353508696</v>
@@ -4010,7 +4010,7 @@
         <v>1067.689752732331</v>
       </c>
       <c r="Z25" s="92" t="n">
-        <v>850.690976620897</v>
+        <v>850.6909766208969</v>
       </c>
       <c r="AA25" s="92" t="n">
         <v>618.1060190396307</v>
@@ -4034,7 +4034,7 @@
         <v>175358.3743668982</v>
       </c>
       <c r="AH25" s="93" t="n">
-        <v>193577.3712679565</v>
+        <v>193577.3712679566</v>
       </c>
     </row>
     <row r="28" ht="1.95" customHeight="1">
@@ -4408,40 +4408,40 @@
         </is>
       </c>
       <c r="C35" s="148" t="n">
-        <v>471.3963863143369</v>
+        <v>471.3963863143368</v>
       </c>
       <c r="D35" s="149" t="n">
-        <v>512.3628247479872</v>
+        <v>512.3628247479871</v>
       </c>
       <c r="E35" s="149" t="n">
-        <v>550.6168724512148</v>
+        <v>550.6168724512147</v>
       </c>
       <c r="F35" s="149" t="n">
         <v>587.3346763286985</v>
       </c>
       <c r="G35" s="150" t="n">
-        <v>621.2270646615179</v>
+        <v>621.2270646615177</v>
       </c>
       <c r="H35" s="148" t="n">
-        <v>467.4031876362209</v>
+        <v>467.4031876362208</v>
       </c>
       <c r="I35" s="149" t="n">
-        <v>509.1355742848724</v>
+        <v>509.1355742848723</v>
       </c>
       <c r="J35" s="149" t="n">
-        <v>548.2613408444638</v>
+        <v>548.2613408444637</v>
       </c>
       <c r="K35" s="149" t="n">
         <v>586.0021398555858</v>
       </c>
       <c r="L35" s="150" t="n">
-        <v>621.0782385390935</v>
+        <v>621.0782385390933</v>
       </c>
       <c r="M35" s="151" t="n">
         <v>54387820.1288207</v>
       </c>
       <c r="N35" s="152" t="n">
-        <v>63294591.51342676</v>
+        <v>63294591.51342675</v>
       </c>
       <c r="O35" s="152" t="n">
         <v>72561292.34221497</v>
@@ -4450,7 +4450,7 @@
         <v>83444391.9342577</v>
       </c>
       <c r="Q35" s="153" t="n">
-        <v>97058088.29658976</v>
+        <v>97058088.29658975</v>
       </c>
       <c r="S35" s="21" t="inlineStr">
         <is>
@@ -4458,40 +4458,40 @@
         </is>
       </c>
       <c r="T35" s="148" t="n">
-        <v>578.4538843336187</v>
+        <v>578.4538843336186</v>
       </c>
       <c r="U35" s="149" t="n">
-        <v>628.7240945584747</v>
+        <v>628.7240945584745</v>
       </c>
       <c r="V35" s="149" t="n">
-        <v>675.6659106772346</v>
+        <v>675.6659106772345</v>
       </c>
       <c r="W35" s="149" t="n">
         <v>720.7225909865474</v>
       </c>
       <c r="X35" s="150" t="n">
-        <v>762.3121836301145</v>
+        <v>762.3121836301142</v>
       </c>
       <c r="Y35" s="148" t="n">
-        <v>573.6087694181816</v>
+        <v>573.6087694181815</v>
       </c>
       <c r="Z35" s="149" t="n">
-        <v>624.8084328677321</v>
+        <v>624.808432867732</v>
       </c>
       <c r="AA35" s="149" t="n">
-        <v>672.8079812661078</v>
+        <v>672.8079812661077</v>
       </c>
       <c r="AB35" s="149" t="n">
         <v>719.1058822122585</v>
       </c>
       <c r="AC35" s="150" t="n">
-        <v>762.131623488219</v>
+        <v>762.1316234882188</v>
       </c>
       <c r="AD35" s="151" t="n">
         <v>54387820.1288207</v>
       </c>
       <c r="AE35" s="152" t="n">
-        <v>63294591.51342676</v>
+        <v>63294591.51342675</v>
       </c>
       <c r="AF35" s="152" t="n">
         <v>72561292.34221497</v>
@@ -4500,7 +4500,7 @@
         <v>83444391.9342577</v>
       </c>
       <c r="AH35" s="153" t="n">
-        <v>97058088.29658976</v>
+        <v>97058088.29658975</v>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1" thickBot="1">
@@ -4528,7 +4528,7 @@
         <v>1037.178381365225</v>
       </c>
       <c r="I36" s="156" t="n">
-        <v>1118.551342955761</v>
+        <v>1118.55134295576</v>
       </c>
       <c r="J36" s="156" t="n">
         <v>1197.720464894825</v>
@@ -4543,13 +4543,13 @@
         <v>26932862.32160074</v>
       </c>
       <c r="N36" s="159" t="n">
-        <v>29834533.18985203</v>
+        <v>29834533.18985202</v>
       </c>
       <c r="O36" s="159" t="n">
-        <v>33261111.66851704</v>
+        <v>33261111.66851703</v>
       </c>
       <c r="P36" s="159" t="n">
-        <v>37595466.99750096</v>
+        <v>37595466.99750097</v>
       </c>
       <c r="Q36" s="160" t="n">
         <v>43046572.51677119</v>
@@ -4593,13 +4593,13 @@
         <v>26932862.32160074</v>
       </c>
       <c r="AE36" s="159" t="n">
-        <v>29834533.18985203</v>
+        <v>29834533.18985202</v>
       </c>
       <c r="AF36" s="159" t="n">
-        <v>33261111.66851704</v>
+        <v>33261111.66851703</v>
       </c>
       <c r="AG36" s="159" t="n">
-        <v>37595466.99750096</v>
+        <v>37595466.99750097</v>
       </c>
       <c r="AH36" s="160" t="n">
         <v>43046572.51677119</v>
@@ -4612,40 +4612,40 @@
         </is>
       </c>
       <c r="C37" s="161" t="n">
-        <v>576.284543261625</v>
+        <v>576.2845432616249</v>
       </c>
       <c r="D37" s="162" t="n">
-        <v>620.7869519334829</v>
+        <v>620.7869519334827</v>
       </c>
       <c r="E37" s="162" t="n">
-        <v>663.8482488933498</v>
+        <v>663.8482488933496</v>
       </c>
       <c r="F37" s="162" t="n">
         <v>705.2985588139469</v>
       </c>
       <c r="G37" s="163" t="n">
-        <v>743.2786492194984</v>
+        <v>743.2786492194982</v>
       </c>
       <c r="H37" s="161" t="n">
-        <v>571.3566223679331</v>
+        <v>571.356622367933</v>
       </c>
       <c r="I37" s="162" t="n">
-        <v>616.7890766042591</v>
+        <v>616.789076604259</v>
       </c>
       <c r="J37" s="162" t="n">
-        <v>660.9011783868787</v>
+        <v>660.9011783868784</v>
       </c>
       <c r="K37" s="162" t="n">
         <v>703.5893892741816</v>
       </c>
       <c r="L37" s="163" t="n">
-        <v>742.9942180130857</v>
+        <v>742.9942180130854</v>
       </c>
       <c r="M37" s="164" t="n">
         <v>81320682.45042145</v>
       </c>
       <c r="N37" s="165" t="n">
-        <v>93129124.70327879</v>
+        <v>93129124.70327878</v>
       </c>
       <c r="O37" s="165" t="n">
         <v>105822404.010732</v>
@@ -4654,7 +4654,7 @@
         <v>121039858.9317587</v>
       </c>
       <c r="Q37" s="166" t="n">
-        <v>140104660.813361</v>
+        <v>140104660.8133609</v>
       </c>
       <c r="S37" s="42" t="inlineStr">
         <is>
@@ -4665,7 +4665,7 @@
         <v>680.7139047714988</v>
       </c>
       <c r="U37" s="162" t="n">
-        <v>734.1609690647616</v>
+        <v>734.1609690647615</v>
       </c>
       <c r="V37" s="162" t="n">
         <v>785.6076788178282</v>
@@ -4674,13 +4674,13 @@
         <v>834.8596987408697</v>
       </c>
       <c r="X37" s="163" t="n">
-        <v>879.9974774222482</v>
+        <v>879.9974774222478</v>
       </c>
       <c r="Y37" s="161" t="n">
         <v>674.9243204519923</v>
       </c>
       <c r="Z37" s="162" t="n">
-        <v>729.4479845418083</v>
+        <v>729.4479845418081</v>
       </c>
       <c r="AA37" s="162" t="n">
         <v>782.121994926207</v>
@@ -4689,13 +4689,13 @@
         <v>832.8273602247499</v>
       </c>
       <c r="AC37" s="163" t="n">
-        <v>879.639641993345</v>
+        <v>879.6396419933446</v>
       </c>
       <c r="AD37" s="164" t="n">
         <v>81320682.45042145</v>
       </c>
       <c r="AE37" s="165" t="n">
-        <v>93129124.70327879</v>
+        <v>93129124.70327878</v>
       </c>
       <c r="AF37" s="165" t="n">
         <v>105822404.010732</v>
@@ -4704,7 +4704,7 @@
         <v>121039858.9317587</v>
       </c>
       <c r="AH37" s="166" t="n">
-        <v>140104660.813361</v>
+        <v>140104660.8133609</v>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1" thickBot="1">
@@ -4723,10 +4723,10 @@
         <v>1366.544511769841</v>
       </c>
       <c r="F38" s="156" t="n">
-        <v>1425.147809083238</v>
+        <v>1425.147809083239</v>
       </c>
       <c r="G38" s="157" t="n">
-        <v>1465.747624492743</v>
+        <v>1465.747624492744</v>
       </c>
       <c r="H38" s="155" t="n">
         <v>1207.707634541153</v>
@@ -4738,10 +4738,10 @@
         <v>1365.410629845278</v>
       </c>
       <c r="K38" s="156" t="n">
-        <v>1425.147809083238</v>
+        <v>1425.147809083239</v>
       </c>
       <c r="L38" s="157" t="n">
-        <v>1465.747624492743</v>
+        <v>1465.747624492744</v>
       </c>
       <c r="M38" s="158" t="n">
         <v>10412893.48068521</v>
@@ -4756,7 +4756,7 @@
         <v>15819557.32501994</v>
       </c>
       <c r="Q38" s="160" t="n">
-        <v>18363624.80980063</v>
+        <v>18363624.80980064</v>
       </c>
       <c r="S38" s="32" t="inlineStr">
         <is>
@@ -4773,10 +4773,10 @@
         <v>1662.9033628385</v>
       </c>
       <c r="W38" s="156" t="n">
-        <v>1734.215800403861</v>
+        <v>1734.215800403862</v>
       </c>
       <c r="X38" s="157" t="n">
-        <v>1783.620389126441</v>
+        <v>1783.620389126442</v>
       </c>
       <c r="Y38" s="155" t="n">
         <v>1469.148430354741</v>
@@ -4788,10 +4788,10 @@
         <v>1661.421065512998</v>
       </c>
       <c r="AB38" s="156" t="n">
-        <v>1734.215800403861</v>
+        <v>1734.215800403862</v>
       </c>
       <c r="AC38" s="157" t="n">
-        <v>1783.620389126441</v>
+        <v>1783.620389126442</v>
       </c>
       <c r="AD38" s="158" t="n">
         <v>10412893.48068521</v>
@@ -4806,7 +4806,7 @@
         <v>15819557.32501994</v>
       </c>
       <c r="AH38" s="160" t="n">
-        <v>18363624.80980063</v>
+        <v>18363624.80980064</v>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1" thickTop="1">
@@ -4819,31 +4819,31 @@
         <v>612.7956328082067</v>
       </c>
       <c r="D39" s="162" t="n">
-        <v>659.9441840122635</v>
+        <v>659.9441840122633</v>
       </c>
       <c r="E39" s="162" t="n">
-        <v>705.4899933935842</v>
+        <v>705.489993393584</v>
       </c>
       <c r="F39" s="162" t="n">
         <v>749.0307178729333</v>
       </c>
       <c r="G39" s="163" t="n">
-        <v>788.3053942328077</v>
+        <v>788.3053942328075</v>
       </c>
       <c r="H39" s="161" t="n">
         <v>607.7037366660645</v>
       </c>
       <c r="I39" s="162" t="n">
-        <v>655.8425152351891</v>
+        <v>655.8425152351889</v>
       </c>
       <c r="J39" s="162" t="n">
-        <v>702.5084555219632</v>
+        <v>702.5084555219631</v>
       </c>
       <c r="K39" s="162" t="n">
-        <v>747.3255934441579</v>
+        <v>747.325593444158</v>
       </c>
       <c r="L39" s="163" t="n">
-        <v>788.0225264373818</v>
+        <v>788.0225264373815</v>
       </c>
       <c r="M39" s="164" t="n">
         <v>91733575.93110666</v>
@@ -4866,34 +4866,34 @@
         </is>
       </c>
       <c r="T39" s="161" t="n">
-        <v>725.0595941468354</v>
+        <v>725.0595941468353</v>
       </c>
       <c r="U39" s="162" t="n">
-        <v>781.7464920270153</v>
+        <v>781.7464920270152</v>
       </c>
       <c r="V39" s="162" t="n">
-        <v>836.2494667843325</v>
+        <v>836.2494667843324</v>
       </c>
       <c r="W39" s="162" t="n">
-        <v>888.0960299879705</v>
+        <v>888.0960299879703</v>
       </c>
       <c r="X39" s="163" t="n">
-        <v>934.8830424697319</v>
+        <v>934.8830424697313</v>
       </c>
       <c r="Y39" s="161" t="n">
-        <v>719.0487202795265</v>
+        <v>719.0487202795264</v>
       </c>
       <c r="Z39" s="162" t="n">
-        <v>776.8899246966695</v>
+        <v>776.8899246966694</v>
       </c>
       <c r="AA39" s="162" t="n">
-        <v>832.709668079255</v>
+        <v>832.7096680792549</v>
       </c>
       <c r="AB39" s="162" t="n">
-        <v>886.0617757815315</v>
+        <v>886.0617757815314</v>
       </c>
       <c r="AC39" s="163" t="n">
-        <v>934.5259703039537</v>
+        <v>934.5259703039532</v>
       </c>
       <c r="AD39" s="164" t="n">
         <v>91733575.93110666</v>
@@ -4918,49 +4918,49 @@
         </is>
       </c>
       <c r="C40" s="155" t="n">
-        <v>7036.394727151741</v>
+        <v>7036.394727151736</v>
       </c>
       <c r="D40" s="156" t="n">
-        <v>7312.518501574925</v>
+        <v>7312.518501574922</v>
       </c>
       <c r="E40" s="156" t="n">
-        <v>7747.254145988882</v>
+        <v>7747.25414598888</v>
       </c>
       <c r="F40" s="156" t="n">
-        <v>7954.575400994801</v>
+        <v>7954.575400994798</v>
       </c>
       <c r="G40" s="157" t="n">
-        <v>8276.723507749737</v>
+        <v>8276.723507749733</v>
       </c>
       <c r="H40" s="155" t="n">
-        <v>7029.829416395053</v>
+        <v>7029.82941639505</v>
       </c>
       <c r="I40" s="156" t="n">
-        <v>7306.380317092007</v>
+        <v>7306.380317092005</v>
       </c>
       <c r="J40" s="156" t="n">
-        <v>7741.305667019601</v>
+        <v>7741.3056670196</v>
       </c>
       <c r="K40" s="156" t="n">
-        <v>7949.174763829446</v>
+        <v>7949.174763829443</v>
       </c>
       <c r="L40" s="157" t="n">
-        <v>8271.766030274404</v>
+        <v>8271.766030274401</v>
       </c>
       <c r="M40" s="158" t="n">
-        <v>65327897.4562111</v>
+        <v>65327897.45621106</v>
       </c>
       <c r="N40" s="159" t="n">
-        <v>76564698.04524426</v>
+        <v>76564698.04524423</v>
       </c>
       <c r="O40" s="159" t="n">
-        <v>90556170.65654339</v>
+        <v>90556170.65654337</v>
       </c>
       <c r="P40" s="159" t="n">
         <v>106558583.5274029</v>
       </c>
       <c r="Q40" s="160" t="n">
-        <v>127360406.7355469</v>
+        <v>127360406.7355468</v>
       </c>
       <c r="S40" s="32" t="inlineStr">
         <is>
@@ -4968,49 +4968,49 @@
         </is>
       </c>
       <c r="T40" s="155" t="n">
-        <v>4512.207364807332</v>
+        <v>4512.20736480733</v>
       </c>
       <c r="U40" s="156" t="n">
-        <v>4689.276414635216</v>
+        <v>4689.276414635215</v>
       </c>
       <c r="V40" s="156" t="n">
-        <v>4968.05801409545</v>
+        <v>4968.058014095449</v>
       </c>
       <c r="W40" s="156" t="n">
-        <v>5101.00628234837</v>
+        <v>5101.006282348369</v>
       </c>
       <c r="X40" s="157" t="n">
-        <v>5307.589215259919</v>
+        <v>5307.589215259916</v>
       </c>
       <c r="Y40" s="155" t="n">
-        <v>4509.074449068287</v>
+        <v>4509.074449068285</v>
       </c>
       <c r="Z40" s="156" t="n">
-        <v>4686.347390508336</v>
+        <v>4686.347390508334</v>
       </c>
       <c r="AA40" s="156" t="n">
-        <v>4965.219565847233</v>
+        <v>4965.219565847232</v>
       </c>
       <c r="AB40" s="156" t="n">
-        <v>5098.429307585334</v>
+        <v>5098.429307585331</v>
       </c>
       <c r="AC40" s="157" t="n">
-        <v>5305.223747568379</v>
+        <v>5305.223747568377</v>
       </c>
       <c r="AD40" s="158" t="n">
-        <v>65327897.4562111</v>
+        <v>65327897.45621106</v>
       </c>
       <c r="AE40" s="159" t="n">
-        <v>76564698.04524426</v>
+        <v>76564698.04524423</v>
       </c>
       <c r="AF40" s="159" t="n">
-        <v>90556170.65654339</v>
+        <v>90556170.65654337</v>
       </c>
       <c r="AG40" s="159" t="n">
         <v>106558583.5274029</v>
       </c>
       <c r="AH40" s="160" t="n">
-        <v>127360406.7355469</v>
+        <v>127360406.7355468</v>
       </c>
     </row>
     <row r="41" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -5020,34 +5020,34 @@
         </is>
       </c>
       <c r="C41" s="179" t="n">
-        <v>987.9252207827519</v>
+        <v>987.9252207827517</v>
       </c>
       <c r="D41" s="180" t="n">
         <v>1070.318322547188</v>
       </c>
       <c r="E41" s="180" t="n">
-        <v>1159.894320001328</v>
+        <v>1159.894320001327</v>
       </c>
       <c r="F41" s="180" t="n">
         <v>1241.224084249557</v>
       </c>
       <c r="G41" s="181" t="n">
-        <v>1320.763229369344</v>
+        <v>1320.763229369343</v>
       </c>
       <c r="H41" s="179" t="n">
-        <v>980.1388657520356</v>
+        <v>980.1388657520353</v>
       </c>
       <c r="I41" s="180" t="n">
-        <v>1064.019244947441</v>
+        <v>1064.01924494744</v>
       </c>
       <c r="J41" s="180" t="n">
-        <v>1155.250394935352</v>
+        <v>1155.250394935351</v>
       </c>
       <c r="K41" s="180" t="n">
         <v>1238.533753411244</v>
       </c>
       <c r="L41" s="181" t="n">
-        <v>1320.266742982562</v>
+        <v>1320.266742982561</v>
       </c>
       <c r="M41" s="182" t="n">
         <v>157061473.3873177</v>
@@ -5062,7 +5062,7 @@
         <v>243417999.7841815</v>
       </c>
       <c r="Q41" s="184" t="n">
-        <v>285828692.3587085</v>
+        <v>285828692.3587084</v>
       </c>
       <c r="S41" s="51" t="inlineStr">
         <is>
@@ -5076,13 +5076,13 @@
         <v>1204.890696428911</v>
       </c>
       <c r="V41" s="186" t="n">
-        <v>1303.508594650394</v>
+        <v>1303.508594650393</v>
       </c>
       <c r="W41" s="186" t="n">
-        <v>1391.007553131772</v>
+        <v>1391.007553131771</v>
       </c>
       <c r="X41" s="187" t="n">
-        <v>1477.136317227518</v>
+        <v>1477.136317227517</v>
       </c>
       <c r="Y41" s="185" t="n">
         <v>1105.565350968856</v>
@@ -5097,7 +5097,7 @@
         <v>1388.117337783274</v>
       </c>
       <c r="AC41" s="187" t="n">
-        <v>1476.560459967475</v>
+        <v>1476.560459967474</v>
       </c>
       <c r="AD41" s="188" t="n">
         <v>157061473.3873177</v>
@@ -5112,7 +5112,7 @@
         <v>243417999.7841815</v>
       </c>
       <c r="AH41" s="190" t="n">
-        <v>285828692.3587085</v>
+        <v>285828692.3587084</v>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1" thickBot="1"/>
@@ -5383,25 +5383,25 @@
         <v>0.2141963817335411</v>
       </c>
       <c r="G46" s="150" t="n">
-        <v>0.2323322653354024</v>
+        <v>0.2323322653354022</v>
       </c>
       <c r="H46" s="148" t="n">
-        <v>0.1572947229889339</v>
+        <v>0.1572947229889338</v>
       </c>
       <c r="I46" s="149" t="n">
         <v>0.173828389278059</v>
       </c>
       <c r="J46" s="149" t="n">
-        <v>0.1935342143360962</v>
+        <v>0.1935342143360961</v>
       </c>
       <c r="K46" s="149" t="n">
         <v>0.2137104160608639</v>
       </c>
       <c r="L46" s="150" t="n">
-        <v>0.2322766059603834</v>
+        <v>0.2322766059603832</v>
       </c>
       <c r="M46" s="151" t="n">
-        <v>18303.07821476197</v>
+        <v>18303.07821476196</v>
       </c>
       <c r="N46" s="152" t="n">
         <v>21609.95508562833</v>
@@ -5413,7 +5413,7 @@
         <v>30431.51979378565</v>
       </c>
       <c r="Q46" s="153" t="n">
-        <v>36298.68498301287</v>
+        <v>36298.68498301286</v>
       </c>
       <c r="S46" s="21" t="inlineStr">
         <is>
@@ -5421,25 +5421,25 @@
         </is>
       </c>
       <c r="T46" s="148" t="n">
-        <v>0.1946665018659329</v>
+        <v>0.1946665018659328</v>
       </c>
       <c r="U46" s="149" t="n">
         <v>0.2146581425014618</v>
       </c>
       <c r="V46" s="149" t="n">
-        <v>0.2385075536699169</v>
+        <v>0.2385075536699168</v>
       </c>
       <c r="W46" s="149" t="n">
         <v>0.2628419152567548</v>
       </c>
       <c r="X46" s="150" t="n">
-        <v>0.2850965880117632</v>
+        <v>0.285096588011763</v>
       </c>
       <c r="Y46" s="148" t="n">
-        <v>0.1930359802335764</v>
+        <v>0.1930359802335763</v>
       </c>
       <c r="Z46" s="149" t="n">
-        <v>0.2133212625051748</v>
+        <v>0.2133212625051747</v>
       </c>
       <c r="AA46" s="149" t="n">
         <v>0.2374987152164185</v>
@@ -5448,10 +5448,10 @@
         <v>0.262252314159244</v>
       </c>
       <c r="AC46" s="150" t="n">
-        <v>0.2850290604535125</v>
+        <v>0.2850290604535123</v>
       </c>
       <c r="AD46" s="151" t="n">
-        <v>18303.07821476197</v>
+        <v>18303.07821476196</v>
       </c>
       <c r="AE46" s="152" t="n">
         <v>21609.95508562833</v>
@@ -5463,7 +5463,7 @@
         <v>30431.51979378565</v>
       </c>
       <c r="AH46" s="153" t="n">
-        <v>36298.68498301287</v>
+        <v>36298.68498301286</v>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1" thickBot="1">
@@ -5544,7 +5544,7 @@
         <v>0.02656465811899818</v>
       </c>
       <c r="AA47" s="156" t="n">
-        <v>0.0264976981769835</v>
+        <v>0.02649769817698349</v>
       </c>
       <c r="AB47" s="156" t="n">
         <v>0.02582824204254794</v>
@@ -5575,49 +5575,49 @@
         </is>
       </c>
       <c r="C48" s="161" t="n">
-        <v>0.1344987440739918</v>
+        <v>0.1344987440739917</v>
       </c>
       <c r="D48" s="162" t="n">
         <v>0.1487184323857965</v>
       </c>
       <c r="E48" s="162" t="n">
-        <v>0.1652451100048923</v>
+        <v>0.1652451100048922</v>
       </c>
       <c r="F48" s="162" t="n">
         <v>0.1817335160110374</v>
       </c>
       <c r="G48" s="163" t="n">
-        <v>0.1967463162252991</v>
+        <v>0.196746316225299</v>
       </c>
       <c r="H48" s="161" t="n">
-        <v>0.1333486192288133</v>
+        <v>0.1333486192288132</v>
       </c>
       <c r="I48" s="162" t="n">
         <v>0.1477606839183324</v>
       </c>
       <c r="J48" s="162" t="n">
-        <v>0.1645115251971508</v>
+        <v>0.1645115251971507</v>
       </c>
       <c r="K48" s="162" t="n">
         <v>0.1812931161462725</v>
       </c>
       <c r="L48" s="163" t="n">
-        <v>0.1966710271097837</v>
+        <v>0.1966710271097836</v>
       </c>
       <c r="M48" s="164" t="n">
         <v>18979.39097050553</v>
       </c>
       <c r="N48" s="165" t="n">
-        <v>22310.41968938968</v>
+        <v>22310.41968938967</v>
       </c>
       <c r="O48" s="165" t="n">
-        <v>26341.31342650401</v>
+        <v>26341.313426504</v>
       </c>
       <c r="P48" s="165" t="n">
         <v>31188.20939906547</v>
       </c>
       <c r="Q48" s="166" t="n">
-        <v>37085.7900061697</v>
+        <v>37085.79000616969</v>
       </c>
       <c r="S48" s="42" t="inlineStr">
         <is>
@@ -5628,22 +5628,22 @@
         <v>0.1588714574006971</v>
       </c>
       <c r="U48" s="162" t="n">
-        <v>0.175878806888724</v>
+        <v>0.1758788068887239</v>
       </c>
       <c r="V48" s="162" t="n">
-        <v>0.1955534680152421</v>
+        <v>0.195553468015242</v>
       </c>
       <c r="W48" s="162" t="n">
         <v>0.2151173946579933</v>
       </c>
       <c r="X48" s="163" t="n">
-        <v>0.2329358742541441</v>
+        <v>0.2329358742541439</v>
       </c>
       <c r="Y48" s="161" t="n">
         <v>0.1575202293853196</v>
       </c>
       <c r="Z48" s="162" t="n">
-        <v>0.1747497437408451</v>
+        <v>0.174749743740845</v>
       </c>
       <c r="AA48" s="162" t="n">
         <v>0.1946858115605125</v>
@@ -5652,22 +5652,22 @@
         <v>0.2145937241929916</v>
       </c>
       <c r="AC48" s="163" t="n">
-        <v>0.2328411549957266</v>
+        <v>0.2328411549957265</v>
       </c>
       <c r="AD48" s="164" t="n">
         <v>18979.39097050553</v>
       </c>
       <c r="AE48" s="165" t="n">
-        <v>22310.41968938968</v>
+        <v>22310.41968938967</v>
       </c>
       <c r="AF48" s="165" t="n">
-        <v>26341.31342650401</v>
+        <v>26341.313426504</v>
       </c>
       <c r="AG48" s="165" t="n">
         <v>31188.20939906547</v>
       </c>
       <c r="AH48" s="166" t="n">
-        <v>37085.7900061697</v>
+        <v>37085.79000616969</v>
       </c>
     </row>
     <row r="49" ht="15" customHeight="1" thickBot="1">
@@ -5695,7 +5695,7 @@
         <v>0.1537348295451925</v>
       </c>
       <c r="I49" s="156" t="n">
-        <v>0.155847198737139</v>
+        <v>0.1558471987371391</v>
       </c>
       <c r="J49" s="156" t="n">
         <v>0.1578533728557786</v>
@@ -5719,7 +5719,7 @@
         <v>1751.331916764923</v>
       </c>
       <c r="Q49" s="160" t="n">
-        <v>1944.252913651833</v>
+        <v>1944.252913651834</v>
       </c>
       <c r="S49" s="32" t="inlineStr">
         <is>
@@ -5736,13 +5736,13 @@
         <v>0.1922461264176759</v>
       </c>
       <c r="W49" s="156" t="n">
-        <v>0.1919894102853147</v>
+        <v>0.1919894102853148</v>
       </c>
       <c r="X49" s="157" t="n">
         <v>0.1888412105085668</v>
       </c>
       <c r="Y49" s="155" t="n">
-        <v>0.187014867719193</v>
+        <v>0.1870148677191931</v>
       </c>
       <c r="Z49" s="156" t="n">
         <v>0.1896093637350641</v>
@@ -5751,7 +5751,7 @@
         <v>0.1920747599237501</v>
       </c>
       <c r="AB49" s="156" t="n">
-        <v>0.1919894102853147</v>
+        <v>0.1919894102853148</v>
       </c>
       <c r="AC49" s="157" t="n">
         <v>0.1888412105085668</v>
@@ -5769,7 +5769,7 @@
         <v>1751.331916764923</v>
       </c>
       <c r="AH49" s="160" t="n">
-        <v>1944.252913651833</v>
+        <v>1944.252913651834</v>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1" thickTop="1">
@@ -5806,7 +5806,7 @@
         <v>0.179867508827052</v>
       </c>
       <c r="L50" s="163" t="n">
-        <v>0.1940864880798702</v>
+        <v>0.1940864880798701</v>
       </c>
       <c r="M50" s="164" t="n">
         <v>20304.89754058993</v>
@@ -5821,7 +5821,7 @@
         <v>32939.54131583039</v>
       </c>
       <c r="Q50" s="166" t="n">
-        <v>39030.04291982154</v>
+        <v>39030.04291982152</v>
       </c>
       <c r="S50" s="42" t="inlineStr">
         <is>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="T50" s="161" t="n">
-        <v>0.1604893368708297</v>
+        <v>0.1604893368708296</v>
       </c>
       <c r="U50" s="162" t="n">
         <v>0.1766843000438436</v>
@@ -5838,10 +5838,10 @@
         <v>0.1953625521188488</v>
       </c>
       <c r="W50" s="162" t="n">
-        <v>0.2137483607070755</v>
+        <v>0.2137483607070754</v>
       </c>
       <c r="X50" s="163" t="n">
-        <v>0.2302575883188191</v>
+        <v>0.2302575883188189</v>
       </c>
       <c r="Y50" s="161" t="n">
         <v>0.1591588515303609</v>
@@ -5853,10 +5853,10 @@
         <v>0.1945355930157594</v>
       </c>
       <c r="AB50" s="162" t="n">
-        <v>0.2132587531790544</v>
+        <v>0.2132587531790543</v>
       </c>
       <c r="AC50" s="163" t="n">
-        <v>0.2301696430122803</v>
+        <v>0.2301696430122802</v>
       </c>
       <c r="AD50" s="164" t="n">
         <v>20304.89754058993</v>
@@ -5871,7 +5871,7 @@
         <v>32939.54131583039</v>
       </c>
       <c r="AH50" s="166" t="n">
-        <v>39030.04291982154</v>
+        <v>39030.04291982152</v>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1" thickBot="1">
@@ -5989,13 +5989,13 @@
         <v>0.1399546015089556</v>
       </c>
       <c r="E52" s="180" t="n">
-        <v>0.1541793590449602</v>
+        <v>0.1541793590449601</v>
       </c>
       <c r="F52" s="180" t="n">
         <v>0.1679635525786576</v>
       </c>
       <c r="G52" s="181" t="n">
-        <v>0.1803508426806719</v>
+        <v>0.1803508426806718</v>
       </c>
       <c r="H52" s="179" t="n">
         <v>0.1267122917888793</v>
@@ -6010,7 +6010,7 @@
         <v>0.1675994946048001</v>
       </c>
       <c r="L52" s="181" t="n">
-        <v>0.1802830472300987</v>
+        <v>0.1802830472300986</v>
       </c>
       <c r="M52" s="182" t="n">
         <v>20304.89754058993</v>
@@ -6025,7 +6025,7 @@
         <v>32939.54131583039</v>
       </c>
       <c r="Q52" s="184" t="n">
-        <v>39030.04291982154</v>
+        <v>39030.04291982152</v>
       </c>
       <c r="S52" s="51" t="inlineStr">
         <is>
@@ -6033,7 +6033,7 @@
         </is>
       </c>
       <c r="T52" s="185" t="n">
-        <v>0.1440097299993103</v>
+        <v>0.1440097299993102</v>
       </c>
       <c r="U52" s="186" t="n">
         <v>0.1575512571617419</v>
@@ -6045,10 +6045,10 @@
         <v>0.1882323854753558</v>
       </c>
       <c r="X52" s="187" t="n">
-        <v>0.2017036616725109</v>
+        <v>0.2017036616725108</v>
       </c>
       <c r="Y52" s="185" t="n">
-        <v>0.1429274200203805</v>
+        <v>0.1429274200203804</v>
       </c>
       <c r="Z52" s="186" t="n">
         <v>0.1566673358028069</v>
@@ -6060,7 +6060,7 @@
         <v>0.1878412789509086</v>
       </c>
       <c r="AC52" s="187" t="n">
-        <v>0.2016250280917122</v>
+        <v>0.2016250280917121</v>
       </c>
       <c r="AD52" s="188" t="n">
         <v>20304.89754058993</v>
@@ -6075,7 +6075,7 @@
         <v>32939.54131583039</v>
       </c>
       <c r="AH52" s="190" t="n">
-        <v>39030.04291982154</v>
+        <v>39030.04291982152</v>
       </c>
     </row>
     <row r="53" ht="15" customHeight="1" thickBot="1"/>
@@ -6334,13 +6334,13 @@
         </is>
       </c>
       <c r="C57" s="148" t="n">
-        <v>0.009019043059663842</v>
+        <v>0.009019043059663841</v>
       </c>
       <c r="D57" s="149" t="n">
-        <v>0.008261989517174093</v>
+        <v>0.008261989517174096</v>
       </c>
       <c r="E57" s="149" t="n">
-        <v>0.007606224730456796</v>
+        <v>0.007606224730456792</v>
       </c>
       <c r="F57" s="149" t="n">
         <v>0.0002754868115454</v>
@@ -6352,10 +6352,10 @@
         <v>0.008942642748016765</v>
       </c>
       <c r="I57" s="149" t="n">
-        <v>0.008209949228129577</v>
+        <v>0.008209949228129581</v>
       </c>
       <c r="J57" s="149" t="n">
-        <v>0.00757368540291879</v>
+        <v>0.007573685402918787</v>
       </c>
       <c r="K57" s="149" t="n">
         <v>0.0002748617910263658</v>
@@ -6367,13 +6367,13 @@
         <v>1040.580933380327</v>
       </c>
       <c r="N57" s="152" t="n">
-        <v>1020.642455539125</v>
+        <v>1020.642455539126</v>
       </c>
       <c r="O57" s="152" t="n">
         <v>1002.362121288176</v>
       </c>
       <c r="P57" s="152" t="n">
-        <v>39.13923424205987</v>
+        <v>39.13923424205988</v>
       </c>
       <c r="Q57" s="153" t="n">
         <v>0</v>
@@ -6390,10 +6390,10 @@
         <v>0.01013834655352266</v>
       </c>
       <c r="V57" s="149" t="n">
-        <v>0.009333652883612167</v>
+        <v>0.009333652883612164</v>
       </c>
       <c r="W57" s="149" t="n">
-        <v>0.0003380518409720223</v>
+        <v>0.0003380518409720224</v>
       </c>
       <c r="X57" s="150" t="n">
         <v>0</v>
@@ -6402,13 +6402,13 @@
         <v>0.01097463268913062</v>
       </c>
       <c r="Z57" s="149" t="n">
-        <v>0.01007520544671494</v>
+        <v>0.01007520544671495</v>
       </c>
       <c r="AA57" s="149" t="n">
-        <v>0.009294173429835097</v>
+        <v>0.009294173429835094</v>
       </c>
       <c r="AB57" s="149" t="n">
-        <v>0.0003372935306536016</v>
+        <v>0.0003372935306536017</v>
       </c>
       <c r="AC57" s="150" t="n">
         <v>0</v>
@@ -6417,13 +6417,13 @@
         <v>1040.580933380327</v>
       </c>
       <c r="AE57" s="152" t="n">
-        <v>1020.642455539125</v>
+        <v>1020.642455539126</v>
       </c>
       <c r="AF57" s="152" t="n">
         <v>1002.362121288176</v>
       </c>
       <c r="AG57" s="152" t="n">
-        <v>39.13923424205987</v>
+        <v>39.13923424205988</v>
       </c>
       <c r="AH57" s="153" t="n">
         <v>0</v>
@@ -6538,28 +6538,28 @@
         </is>
       </c>
       <c r="C59" s="161" t="n">
-        <v>0.007374147508973951</v>
+        <v>0.007374147508973949</v>
       </c>
       <c r="D59" s="162" t="n">
-        <v>0.006803473360313153</v>
+        <v>0.006803473360313156</v>
       </c>
       <c r="E59" s="162" t="n">
-        <v>0.006288047840102894</v>
+        <v>0.006288047840102891</v>
       </c>
       <c r="F59" s="162" t="n">
-        <v>0.0002280640918424211</v>
+        <v>0.0002280640918424212</v>
       </c>
       <c r="G59" s="163" t="n">
         <v>0</v>
       </c>
       <c r="H59" s="161" t="n">
-        <v>0.007311089743487187</v>
+        <v>0.007311089743487185</v>
       </c>
       <c r="I59" s="162" t="n">
-        <v>0.006759658911224761</v>
+        <v>0.006759658911224766</v>
       </c>
       <c r="J59" s="162" t="n">
-        <v>0.006260132845427923</v>
+        <v>0.006260132845427919</v>
       </c>
       <c r="K59" s="162" t="n">
         <v>0.000227511417809531</v>
@@ -6571,13 +6571,13 @@
         <v>1040.580933380327</v>
       </c>
       <c r="N59" s="165" t="n">
-        <v>1020.642455539125</v>
+        <v>1020.642455539126</v>
       </c>
       <c r="O59" s="165" t="n">
         <v>1002.362121288176</v>
       </c>
       <c r="P59" s="165" t="n">
-        <v>39.13923424205987</v>
+        <v>39.13923424205988</v>
       </c>
       <c r="Q59" s="166" t="n">
         <v>0</v>
@@ -6591,10 +6591,10 @@
         <v>0.008710427520378268</v>
       </c>
       <c r="U59" s="162" t="n">
-        <v>0.008045988369531631</v>
+        <v>0.008045988369531635</v>
       </c>
       <c r="V59" s="162" t="n">
-        <v>0.007441367324827147</v>
+        <v>0.007441367324827145</v>
       </c>
       <c r="W59" s="162" t="n">
         <v>0.0002699587524031797</v>
@@ -6606,13 +6606,13 @@
         <v>0.008636343894005001</v>
       </c>
       <c r="Z59" s="162" t="n">
-        <v>0.007994336728739868</v>
+        <v>0.007994336728739872</v>
       </c>
       <c r="AA59" s="162" t="n">
-        <v>0.007408350521510232</v>
+        <v>0.00740835052151023</v>
       </c>
       <c r="AB59" s="162" t="n">
-        <v>0.0002693015790229098</v>
+        <v>0.0002693015790229099</v>
       </c>
       <c r="AC59" s="163" t="n">
         <v>0</v>
@@ -6621,13 +6621,13 @@
         <v>1040.580933380327</v>
       </c>
       <c r="AE59" s="165" t="n">
-        <v>1020.642455539125</v>
+        <v>1020.642455539126</v>
       </c>
       <c r="AF59" s="165" t="n">
         <v>1002.362121288176</v>
       </c>
       <c r="AG59" s="165" t="n">
-        <v>39.13923424205987</v>
+        <v>39.13923424205988</v>
       </c>
       <c r="AH59" s="166" t="n">
         <v>0</v>
@@ -6745,10 +6745,10 @@
         <v>0.00695125470784925</v>
       </c>
       <c r="D61" s="162" t="n">
-        <v>0.006408469559538246</v>
+        <v>0.00640846955953825</v>
       </c>
       <c r="E61" s="162" t="n">
-        <v>0.005915418447581365</v>
+        <v>0.005915418447581363</v>
       </c>
       <c r="F61" s="162" t="n">
         <v>0.0002142087809750903</v>
@@ -6760,10 +6760,10 @@
         <v>0.00689349472208084</v>
       </c>
       <c r="I61" s="162" t="n">
-        <v>0.0063686397979645</v>
+        <v>0.006368639797964502</v>
       </c>
       <c r="J61" s="162" t="n">
-        <v>0.005890418739161533</v>
+        <v>0.005890418739161531</v>
       </c>
       <c r="K61" s="162" t="n">
         <v>0.0002137211472685101</v>
@@ -6775,13 +6775,13 @@
         <v>1040.580933380327</v>
       </c>
       <c r="N61" s="165" t="n">
-        <v>1020.642455539125</v>
+        <v>1020.642455539126</v>
       </c>
       <c r="O61" s="165" t="n">
         <v>1002.362121288176</v>
       </c>
       <c r="P61" s="165" t="n">
-        <v>39.13923424205987</v>
+        <v>39.13923424205988</v>
       </c>
       <c r="Q61" s="166" t="n">
         <v>0</v>
@@ -6795,10 +6795,10 @@
         <v>0.00822472231759834</v>
       </c>
       <c r="U61" s="162" t="n">
-        <v>0.007591245924727842</v>
+        <v>0.007591245924727846</v>
       </c>
       <c r="V61" s="162" t="n">
-        <v>0.007011815289967381</v>
+        <v>0.007011815289967379</v>
       </c>
       <c r="W61" s="162" t="n">
         <v>0.0002539788601898336</v>
@@ -6807,13 +6807,13 @@
         <v>0</v>
       </c>
       <c r="Y61" s="161" t="n">
-        <v>0.008156537896836491</v>
+        <v>0.008156537896836489</v>
       </c>
       <c r="Z61" s="162" t="n">
-        <v>0.007544085627456716</v>
+        <v>0.00754408562745672</v>
       </c>
       <c r="AA61" s="162" t="n">
-        <v>0.006982134655575934</v>
+        <v>0.006982134655575932</v>
       </c>
       <c r="AB61" s="162" t="n">
         <v>0.0002533971015204533</v>
@@ -6825,13 +6825,13 @@
         <v>1040.580933380327</v>
       </c>
       <c r="AE61" s="165" t="n">
-        <v>1020.642455539125</v>
+        <v>1020.642455539126</v>
       </c>
       <c r="AF61" s="165" t="n">
         <v>1002.362121288176</v>
       </c>
       <c r="AG61" s="165" t="n">
-        <v>39.13923424205987</v>
+        <v>39.13923424205988</v>
       </c>
       <c r="AH61" s="166" t="n">
         <v>0</v>
@@ -6949,10 +6949,10 @@
         <v>0.006545310738407288</v>
       </c>
       <c r="D63" s="180" t="n">
-        <v>0.006013153393301668</v>
+        <v>0.006013153393301671</v>
       </c>
       <c r="E63" s="180" t="n">
-        <v>0.005533697095086828</v>
+        <v>0.005533697095086824</v>
       </c>
       <c r="F63" s="180" t="n">
         <v>0.0001995766961498411</v>
@@ -6961,13 +6961,13 @@
         <v>0</v>
       </c>
       <c r="H63" s="179" t="n">
-        <v>0.006493723723394938</v>
+        <v>0.006493723723394937</v>
       </c>
       <c r="I63" s="180" t="n">
-        <v>0.005977764557059522</v>
+        <v>0.005977764557059524</v>
       </c>
       <c r="J63" s="180" t="n">
-        <v>0.005511541564014511</v>
+        <v>0.00551154156401451</v>
       </c>
       <c r="K63" s="180" t="n">
         <v>0.0001991441172568967</v>
@@ -6979,13 +6979,13 @@
         <v>1040.580933380327</v>
       </c>
       <c r="N63" s="183" t="n">
-        <v>1020.642455539125</v>
+        <v>1020.642455539126</v>
       </c>
       <c r="O63" s="183" t="n">
         <v>1002.362121288176</v>
       </c>
       <c r="P63" s="183" t="n">
-        <v>39.13923424205987</v>
+        <v>39.13923424205988</v>
       </c>
       <c r="Q63" s="184" t="n">
         <v>0</v>
@@ -6999,10 +6999,10 @@
         <v>0.007380179040990981</v>
       </c>
       <c r="U63" s="186" t="n">
-        <v>0.006769194198737725</v>
+        <v>0.006769194198737729</v>
       </c>
       <c r="V63" s="186" t="n">
-        <v>0.006218861149030665</v>
+        <v>0.006218861149030663</v>
       </c>
       <c r="W63" s="186" t="n">
         <v>0.0002236604133743971</v>
@@ -7014,10 +7014,10 @@
         <v>0.007324713056696786</v>
       </c>
       <c r="Z63" s="186" t="n">
-        <v>0.006731216492670293</v>
+        <v>0.006731216492670296</v>
       </c>
       <c r="AA63" s="186" t="n">
-        <v>0.006195103811132299</v>
+        <v>0.006195103811132297</v>
       </c>
       <c r="AB63" s="186" t="n">
         <v>0.0002231956950066711</v>
@@ -7029,13 +7029,13 @@
         <v>1040.580933380327</v>
       </c>
       <c r="AE63" s="189" t="n">
-        <v>1020.642455539125</v>
+        <v>1020.642455539126</v>
       </c>
       <c r="AF63" s="189" t="n">
         <v>1002.362121288176</v>
       </c>
       <c r="AG63" s="189" t="n">
-        <v>39.13923424205987</v>
+        <v>39.13923424205988</v>
       </c>
       <c r="AH63" s="190" t="n">
         <v>0</v>
@@ -7300,10 +7300,10 @@
         <v>0.003828059914953592</v>
       </c>
       <c r="D68" s="149" t="n">
-        <v>0.005537928342499779</v>
+        <v>0.00553792834249978</v>
       </c>
       <c r="E68" s="149" t="n">
-        <v>0.007285441474027149</v>
+        <v>0.007285441474027146</v>
       </c>
       <c r="F68" s="149" t="n">
         <v>0.008863885829097015</v>
@@ -7312,13 +7312,13 @@
         <v>0.0102542697994211</v>
       </c>
       <c r="H68" s="148" t="n">
-        <v>0.00379563242031016</v>
+        <v>0.003795632420310159</v>
       </c>
       <c r="I68" s="149" t="n">
-        <v>0.005503046261004463</v>
+        <v>0.005503046261004465</v>
       </c>
       <c r="J68" s="149" t="n">
-        <v>0.007254274452964375</v>
+        <v>0.007254274452964372</v>
       </c>
       <c r="K68" s="149" t="n">
         <v>0.008843775572310189</v>
@@ -7330,16 +7330,16 @@
         <v>441.6661649120337</v>
       </c>
       <c r="N68" s="152" t="n">
-        <v>684.12635604771</v>
+        <v>684.1263560477103</v>
       </c>
       <c r="O68" s="152" t="n">
-        <v>960.0887206481665</v>
+        <v>960.0887206481663</v>
       </c>
       <c r="P68" s="152" t="n">
         <v>1259.318737669335</v>
       </c>
       <c r="Q68" s="153" t="n">
-        <v>1602.087031014246</v>
+        <v>1602.087031014247</v>
       </c>
       <c r="S68" s="21" t="inlineStr">
         <is>
@@ -7347,13 +7347,13 @@
         </is>
       </c>
       <c r="T68" s="148" t="n">
-        <v>0.004697439758882982</v>
+        <v>0.004697439758882981</v>
       </c>
       <c r="U68" s="149" t="n">
-        <v>0.006795631561638909</v>
+        <v>0.006795631561638911</v>
       </c>
       <c r="V68" s="149" t="n">
-        <v>0.008940017450464867</v>
+        <v>0.008940017450464863</v>
       </c>
       <c r="W68" s="149" t="n">
         <v>0.01087693783191597</v>
@@ -7362,13 +7362,13 @@
         <v>0.01258308796734119</v>
       </c>
       <c r="Y68" s="148" t="n">
-        <v>0.004658094123808977</v>
+        <v>0.004658094123808976</v>
       </c>
       <c r="Z68" s="149" t="n">
-        <v>0.006753308713825996</v>
+        <v>0.006753308713825997</v>
       </c>
       <c r="AA68" s="149" t="n">
-        <v>0.008902202994527521</v>
+        <v>0.008902202994527519</v>
       </c>
       <c r="AB68" s="149" t="n">
         <v>0.010852538928579</v>
@@ -7380,16 +7380,16 @@
         <v>441.6661649120337</v>
       </c>
       <c r="AE68" s="152" t="n">
-        <v>684.12635604771</v>
+        <v>684.1263560477103</v>
       </c>
       <c r="AF68" s="152" t="n">
-        <v>960.0887206481665</v>
+        <v>960.0887206481663</v>
       </c>
       <c r="AG68" s="152" t="n">
         <v>1259.318737669335</v>
       </c>
       <c r="AH68" s="153" t="n">
-        <v>1602.087031014246</v>
+        <v>1602.087031014247</v>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1" thickBot="1">
@@ -7501,13 +7501,13 @@
         </is>
       </c>
       <c r="C70" s="161" t="n">
-        <v>0.003129897296122922</v>
+        <v>0.003129897296122921</v>
       </c>
       <c r="D70" s="162" t="n">
-        <v>0.004560299655573444</v>
+        <v>0.004560299655573445</v>
       </c>
       <c r="E70" s="162" t="n">
-        <v>0.006022857087237448</v>
+        <v>0.006022857087237444</v>
       </c>
       <c r="F70" s="162" t="n">
         <v>0.007338043010000027</v>
@@ -7516,13 +7516,13 @@
         <v>0.00849933954681675</v>
       </c>
       <c r="H70" s="161" t="n">
-        <v>0.003103132937333463</v>
+        <v>0.003103132937333462</v>
       </c>
       <c r="I70" s="162" t="n">
-        <v>0.004530931271734026</v>
+        <v>0.004530931271734027</v>
       </c>
       <c r="J70" s="162" t="n">
-        <v>0.005996119373436022</v>
+        <v>0.005996119373436018</v>
       </c>
       <c r="K70" s="162" t="n">
         <v>0.007320260527053697</v>
@@ -7534,16 +7534,16 @@
         <v>441.6661649120337</v>
       </c>
       <c r="N70" s="165" t="n">
-        <v>684.12635604771</v>
+        <v>684.1263560477103</v>
       </c>
       <c r="O70" s="165" t="n">
-        <v>960.0887206481665</v>
+        <v>960.0887206481663</v>
       </c>
       <c r="P70" s="165" t="n">
         <v>1259.318737669335</v>
       </c>
       <c r="Q70" s="166" t="n">
-        <v>1602.087031014246</v>
+        <v>1602.087031014247</v>
       </c>
       <c r="S70" s="42" t="inlineStr">
         <is>
@@ -7554,10 +7554,10 @@
         <v>0.003697070544212643</v>
       </c>
       <c r="U70" s="162" t="n">
-        <v>0.005393144949219607</v>
+        <v>0.005393144949219608</v>
       </c>
       <c r="V70" s="162" t="n">
-        <v>0.007127536728527653</v>
+        <v>0.007127536728527651</v>
       </c>
       <c r="W70" s="162" t="n">
         <v>0.008686018566347627</v>
@@ -7569,10 +7569,10 @@
         <v>0.003665626347905139</v>
       </c>
       <c r="Z70" s="162" t="n">
-        <v>0.00535852337473289</v>
+        <v>0.005358523374732891</v>
       </c>
       <c r="AA70" s="162" t="n">
-        <v>0.007095912368644927</v>
+        <v>0.007095912368644926</v>
       </c>
       <c r="AB70" s="162" t="n">
         <v>0.008664873779851472</v>
@@ -7584,16 +7584,16 @@
         <v>441.6661649120337</v>
       </c>
       <c r="AE70" s="165" t="n">
-        <v>684.12635604771</v>
+        <v>684.1263560477103</v>
       </c>
       <c r="AF70" s="165" t="n">
-        <v>960.0887206481665</v>
+        <v>960.0887206481663</v>
       </c>
       <c r="AG70" s="165" t="n">
         <v>1259.318737669335</v>
       </c>
       <c r="AH70" s="166" t="n">
-        <v>1602.087031014246</v>
+        <v>1602.087031014247</v>
       </c>
     </row>
     <row r="71" ht="15" customHeight="1" thickBot="1">
@@ -7612,7 +7612,7 @@
         <v>0.01662674882489198</v>
       </c>
       <c r="F71" s="156" t="n">
-        <v>0.02013203964405094</v>
+        <v>0.02013203964405095</v>
       </c>
       <c r="G71" s="157" t="n">
         <v>0.0230512031623378</v>
@@ -7621,13 +7621,13 @@
         <v>0.008652558177116375</v>
       </c>
       <c r="I71" s="156" t="n">
-        <v>0.01263655807645514</v>
+        <v>0.01263655807645515</v>
       </c>
       <c r="J71" s="156" t="n">
         <v>0.01661295288206362</v>
       </c>
       <c r="K71" s="156" t="n">
-        <v>0.02013203964405094</v>
+        <v>0.02013203964405095</v>
       </c>
       <c r="L71" s="157" t="n">
         <v>0.0230512031623378</v>
@@ -7636,16 +7636,16 @@
         <v>74.60263068385404</v>
       </c>
       <c r="N71" s="159" t="n">
-        <v>117.1463995275705</v>
+        <v>117.1463995275706</v>
       </c>
       <c r="O71" s="159" t="n">
-        <v>166.9582110181674</v>
+        <v>166.9582110181673</v>
       </c>
       <c r="P71" s="159" t="n">
-        <v>223.4715256823136</v>
+        <v>223.4715256823137</v>
       </c>
       <c r="Q71" s="160" t="n">
-        <v>288.7970884033706</v>
+        <v>288.7970884033705</v>
       </c>
       <c r="S71" s="32" t="inlineStr">
         <is>
@@ -7662,10 +7662,10 @@
         <v>0.02023254734540302</v>
       </c>
       <c r="W71" s="156" t="n">
-        <v>0.02449802120351917</v>
+        <v>0.02449802120351918</v>
       </c>
       <c r="X71" s="157" t="n">
-        <v>0.02805025590163947</v>
+        <v>0.02805025590163946</v>
       </c>
       <c r="Y71" s="155" t="n">
         <v>0.01052563708375766</v>
@@ -7677,25 +7677,25 @@
         <v>0.0202145122319452</v>
       </c>
       <c r="AB71" s="156" t="n">
-        <v>0.02449802120351917</v>
+        <v>0.02449802120351918</v>
       </c>
       <c r="AC71" s="157" t="n">
-        <v>0.02805025590163947</v>
+        <v>0.02805025590163946</v>
       </c>
       <c r="AD71" s="158" t="n">
         <v>74.60263068385404</v>
       </c>
       <c r="AE71" s="159" t="n">
-        <v>117.1463995275705</v>
+        <v>117.1463995275706</v>
       </c>
       <c r="AF71" s="159" t="n">
-        <v>166.9582110181674</v>
+        <v>166.9582110181673</v>
       </c>
       <c r="AG71" s="159" t="n">
-        <v>223.4715256823136</v>
+        <v>223.4715256823137</v>
       </c>
       <c r="AH71" s="160" t="n">
-        <v>288.7970884033706</v>
+        <v>288.7970884033705</v>
       </c>
     </row>
     <row r="72" ht="15" customHeight="1" thickTop="1">
@@ -7708,13 +7708,13 @@
         <v>0.003448761918252369</v>
       </c>
       <c r="D72" s="162" t="n">
-        <v>0.005031078253823112</v>
+        <v>0.005031078253823113</v>
       </c>
       <c r="E72" s="162" t="n">
-        <v>0.006651243167789534</v>
+        <v>0.006651243167789532</v>
       </c>
       <c r="F72" s="162" t="n">
-        <v>0.00811530171464012</v>
+        <v>0.008115301714640121</v>
       </c>
       <c r="G72" s="163" t="n">
         <v>0.009406261608399682</v>
@@ -7723,22 +7723,22 @@
         <v>0.003420105158043028</v>
       </c>
       <c r="I72" s="162" t="n">
-        <v>0.004999809220640239</v>
+        <v>0.00499980922064024</v>
       </c>
       <c r="J72" s="162" t="n">
-        <v>0.006623133721044963</v>
+        <v>0.006623133721044961</v>
       </c>
       <c r="K72" s="162" t="n">
-        <v>0.008096827707005545</v>
+        <v>0.008096827707005547</v>
       </c>
       <c r="L72" s="163" t="n">
-        <v>0.009402886357508551</v>
+        <v>0.00940288635750855</v>
       </c>
       <c r="M72" s="164" t="n">
         <v>516.2687955958877</v>
       </c>
       <c r="N72" s="165" t="n">
-        <v>801.2727555752806</v>
+        <v>801.2727555752808</v>
       </c>
       <c r="O72" s="165" t="n">
         <v>1127.046931666334</v>
@@ -7758,25 +7758,25 @@
         <v>0.004080573984018177</v>
       </c>
       <c r="U72" s="162" t="n">
-        <v>0.005959636998583708</v>
+        <v>0.00595963699858371</v>
       </c>
       <c r="V72" s="162" t="n">
-        <v>0.007884021892021233</v>
+        <v>0.007884021892021231</v>
       </c>
       <c r="W72" s="162" t="n">
         <v>0.009621991545811469</v>
       </c>
       <c r="X72" s="163" t="n">
-        <v>0.01115526360096161</v>
+        <v>0.0111552636009616</v>
       </c>
       <c r="Y72" s="161" t="n">
         <v>0.004046745295008114</v>
       </c>
       <c r="Z72" s="162" t="n">
-        <v>0.005922613003409781</v>
+        <v>0.005922613003409783</v>
       </c>
       <c r="AA72" s="162" t="n">
-        <v>0.007850649254318401</v>
+        <v>0.007850649254318399</v>
       </c>
       <c r="AB72" s="162" t="n">
         <v>0.009599951613061571</v>
@@ -7788,7 +7788,7 @@
         <v>516.2687955958877</v>
       </c>
       <c r="AE72" s="165" t="n">
-        <v>801.2727555752806</v>
+        <v>801.2727555752808</v>
       </c>
       <c r="AF72" s="165" t="n">
         <v>1127.046931666334</v>
@@ -7912,37 +7912,37 @@
         <v>0.003247358839010462</v>
       </c>
       <c r="D74" s="180" t="n">
-        <v>0.004720728559740945</v>
+        <v>0.004720728559740947</v>
       </c>
       <c r="E74" s="180" t="n">
-        <v>0.006222039120725584</v>
+        <v>0.00622203912072558</v>
       </c>
       <c r="F74" s="180" t="n">
         <v>0.007560965041182682</v>
       </c>
       <c r="G74" s="181" t="n">
-        <v>0.008737437082737052</v>
+        <v>0.008737437082737051</v>
       </c>
       <c r="H74" s="179" t="n">
-        <v>0.003221764706680653</v>
+        <v>0.003221764706680652</v>
       </c>
       <c r="I74" s="180" t="n">
         <v>0.004692945950680883</v>
       </c>
       <c r="J74" s="180" t="n">
-        <v>0.006197127641346852</v>
+        <v>0.00619712764134685</v>
       </c>
       <c r="K74" s="180" t="n">
-        <v>0.007544576785688911</v>
+        <v>0.007544576785688912</v>
       </c>
       <c r="L74" s="181" t="n">
-        <v>0.008734152604133712</v>
+        <v>0.00873415260413371</v>
       </c>
       <c r="M74" s="182" t="n">
         <v>516.2687955958877</v>
       </c>
       <c r="N74" s="183" t="n">
-        <v>801.2727555752806</v>
+        <v>801.2727555752808</v>
       </c>
       <c r="O74" s="183" t="n">
         <v>1127.046931666334</v>
@@ -7962,37 +7962,37 @@
         <v>0.003661566364085816</v>
       </c>
       <c r="U74" s="186" t="n">
-        <v>0.005314271280025994</v>
+        <v>0.005314271280025995</v>
       </c>
       <c r="V74" s="186" t="n">
-        <v>0.006992431405395187</v>
+        <v>0.006992431405395185</v>
       </c>
       <c r="W74" s="186" t="n">
-        <v>0.008473376898426177</v>
+        <v>0.008473376898426178</v>
       </c>
       <c r="X74" s="187" t="n">
-        <v>0.009771914713709947</v>
+        <v>0.009771914713709945</v>
       </c>
       <c r="Y74" s="185" t="n">
         <v>0.003634047738681944</v>
       </c>
       <c r="Z74" s="186" t="n">
-        <v>0.005284456234584831</v>
+        <v>0.005284456234584832</v>
       </c>
       <c r="AA74" s="186" t="n">
-        <v>0.006965718868863476</v>
+        <v>0.006965718868863474</v>
       </c>
       <c r="AB74" s="186" t="n">
-        <v>0.008455771038623118</v>
+        <v>0.008455771038623119</v>
       </c>
       <c r="AC74" s="187" t="n">
-        <v>0.009768105161425037</v>
+        <v>0.009768105161425036</v>
       </c>
       <c r="AD74" s="188" t="n">
         <v>516.2687955958877</v>
       </c>
       <c r="AE74" s="189" t="n">
-        <v>801.2727555752806</v>
+        <v>801.2727555752808</v>
       </c>
       <c r="AF74" s="189" t="n">
         <v>1127.046931666334</v>
@@ -8260,40 +8260,40 @@
         </is>
       </c>
       <c r="C79" s="148" t="n">
-        <v>471.5678719674213</v>
+        <v>471.5678719674212</v>
       </c>
       <c r="D79" s="149" t="n">
-        <v>512.5515548986774</v>
+        <v>512.5515548986773</v>
       </c>
       <c r="E79" s="149" t="n">
-        <v>550.8261298256523</v>
+        <v>550.8261298256522</v>
       </c>
       <c r="F79" s="149" t="n">
         <v>587.5580120830728</v>
       </c>
       <c r="G79" s="150" t="n">
-        <v>621.4696511966529</v>
+        <v>621.4696511966526</v>
       </c>
       <c r="H79" s="148" t="n">
         <v>467.5732206343781</v>
       </c>
       <c r="I79" s="149" t="n">
-        <v>509.3231156696397</v>
+        <v>509.3231156696395</v>
       </c>
       <c r="J79" s="149" t="n">
-        <v>548.4697030186558</v>
+        <v>548.4697030186557</v>
       </c>
       <c r="K79" s="149" t="n">
         <v>586.22496890901</v>
       </c>
       <c r="L79" s="150" t="n">
-        <v>621.3207669582584</v>
+        <v>621.3207669582582</v>
       </c>
       <c r="M79" s="151" t="n">
         <v>54407605.45413376</v>
       </c>
       <c r="N79" s="152" t="n">
-        <v>63317906.23732398</v>
+        <v>63317906.23732397</v>
       </c>
       <c r="O79" s="152" t="n">
         <v>72588868.65939851</v>
@@ -8302,7 +8302,7 @@
         <v>83476121.9120234</v>
       </c>
       <c r="Q79" s="153" t="n">
-        <v>97095989.06860378</v>
+        <v>97095989.06860377</v>
       </c>
       <c r="S79" s="21" t="inlineStr">
         <is>
@@ -8310,40 +8310,40 @@
         </is>
       </c>
       <c r="T79" s="148" t="n">
-        <v>578.6643156076252</v>
+        <v>578.6643156076251</v>
       </c>
       <c r="U79" s="149" t="n">
-        <v>628.9556866790913</v>
+        <v>628.9556866790912</v>
       </c>
       <c r="V79" s="149" t="n">
-        <v>675.9226919012385</v>
+        <v>675.9226919012384</v>
       </c>
       <c r="W79" s="149" t="n">
         <v>720.996647891477</v>
       </c>
       <c r="X79" s="150" t="n">
-        <v>762.6098633060935</v>
+        <v>762.6098633060933</v>
       </c>
       <c r="Y79" s="148" t="n">
-        <v>573.8174381252281</v>
+        <v>573.817438125228</v>
       </c>
       <c r="Z79" s="149" t="n">
-        <v>625.0385826443979</v>
+        <v>625.0385826443977</v>
       </c>
       <c r="AA79" s="149" t="n">
-        <v>673.0636763577486</v>
+        <v>673.0636763577485</v>
       </c>
       <c r="AB79" s="149" t="n">
         <v>719.3793243588769</v>
       </c>
       <c r="AC79" s="150" t="n">
-        <v>762.4292326562281</v>
+        <v>762.4292326562279</v>
       </c>
       <c r="AD79" s="151" t="n">
         <v>54407605.45413376</v>
       </c>
       <c r="AE79" s="152" t="n">
-        <v>63317906.23732398</v>
+        <v>63317906.23732397</v>
       </c>
       <c r="AF79" s="152" t="n">
         <v>72588868.65939851</v>
@@ -8352,7 +8352,7 @@
         <v>83476121.9120234</v>
       </c>
       <c r="AH79" s="153" t="n">
-        <v>97095989.06860378</v>
+        <v>97095989.06860377</v>
       </c>
     </row>
     <row r="80" ht="15" customHeight="1" thickBot="1">
@@ -8365,7 +8365,7 @@
         <v>1046.529579090465</v>
       </c>
       <c r="D80" s="156" t="n">
-        <v>1126.574450002636</v>
+        <v>1126.574450002635</v>
       </c>
       <c r="E80" s="156" t="n">
         <v>1204.017802653421</v>
@@ -8383,7 +8383,7 @@
         <v>1118.577604657871</v>
       </c>
       <c r="J80" s="156" t="n">
-        <v>1197.746659998266</v>
+        <v>1197.746659998265</v>
       </c>
       <c r="K80" s="156" t="n">
         <v>1268.603960540155</v>
@@ -8395,13 +8395,13 @@
         <v>26933538.63435649</v>
       </c>
       <c r="N80" s="159" t="n">
-        <v>29835233.6544558</v>
+        <v>29835233.65445578</v>
       </c>
       <c r="O80" s="159" t="n">
         <v>33261839.11560193</v>
       </c>
       <c r="P80" s="159" t="n">
-        <v>37596223.68710624</v>
+        <v>37596223.68710625</v>
       </c>
       <c r="Q80" s="160" t="n">
         <v>43047359.62179434</v>
@@ -8415,10 +8415,10 @@
         <v>1058.663462971985</v>
       </c>
       <c r="U80" s="156" t="n">
-        <v>1139.636406237165</v>
+        <v>1139.636406237164</v>
       </c>
       <c r="V80" s="156" t="n">
-        <v>1217.977668194323</v>
+        <v>1217.977668194322</v>
       </c>
       <c r="W80" s="156" t="n">
         <v>1287.388379928213</v>
@@ -8430,10 +8430,10 @@
         <v>1049.15420339551</v>
       </c>
       <c r="Z80" s="156" t="n">
-        <v>1131.481559061162</v>
+        <v>1131.481559061161</v>
       </c>
       <c r="AA80" s="156" t="n">
-        <v>1211.582521945054</v>
+        <v>1211.582521945053</v>
       </c>
       <c r="AB80" s="156" t="n">
         <v>1283.279641349469</v>
@@ -8445,13 +8445,13 @@
         <v>26933538.63435649</v>
       </c>
       <c r="AE80" s="159" t="n">
-        <v>29835233.6544558</v>
+        <v>29835233.65445578</v>
       </c>
       <c r="AF80" s="159" t="n">
         <v>33261839.11560193</v>
       </c>
       <c r="AG80" s="159" t="n">
-        <v>37596223.68710624</v>
+        <v>37596223.68710625</v>
       </c>
       <c r="AH80" s="160" t="n">
         <v>43047359.62179434</v>
@@ -8464,43 +8464,43 @@
         </is>
       </c>
       <c r="C81" s="161" t="n">
-        <v>576.4295460505041</v>
+        <v>576.429546050504</v>
       </c>
       <c r="D81" s="162" t="n">
-        <v>620.9470341388846</v>
+        <v>620.9470341388843</v>
       </c>
       <c r="E81" s="162" t="n">
-        <v>664.0258049082821</v>
+        <v>664.0258049082818</v>
       </c>
       <c r="F81" s="162" t="n">
         <v>705.4878584370598</v>
       </c>
       <c r="G81" s="163" t="n">
-        <v>743.4838948752705</v>
+        <v>743.4838948752703</v>
       </c>
       <c r="H81" s="161" t="n">
-        <v>571.5003852098428</v>
+        <v>571.5003852098426</v>
       </c>
       <c r="I81" s="162" t="n">
-        <v>616.9481278783604</v>
+        <v>616.9481278783603</v>
       </c>
       <c r="J81" s="162" t="n">
-        <v>661.0779461642948</v>
+        <v>661.0779461642944</v>
       </c>
       <c r="K81" s="162" t="n">
         <v>703.7782301622727</v>
       </c>
       <c r="L81" s="163" t="n">
-        <v>743.1993851272912</v>
+        <v>743.199385127291</v>
       </c>
       <c r="M81" s="164" t="n">
         <v>81341144.08849025</v>
       </c>
       <c r="N81" s="165" t="n">
-        <v>93153139.89177978</v>
+        <v>93153139.89177975</v>
       </c>
       <c r="O81" s="165" t="n">
-        <v>105850707.7750005</v>
+        <v>105850707.7750004</v>
       </c>
       <c r="P81" s="165" t="n">
         <v>121072345.5991296</v>
@@ -8517,40 +8517,40 @@
         <v>680.8851837269641</v>
       </c>
       <c r="U81" s="162" t="n">
-        <v>734.3502870049692</v>
+        <v>734.3502870049689</v>
       </c>
       <c r="V81" s="162" t="n">
-        <v>785.8178011898968</v>
+        <v>785.8178011898967</v>
       </c>
       <c r="W81" s="162" t="n">
         <v>835.0837721128464</v>
       </c>
       <c r="X81" s="163" t="n">
-        <v>880.2404760063201</v>
+        <v>880.2404760063198</v>
       </c>
       <c r="Y81" s="161" t="n">
         <v>675.0941426516196</v>
       </c>
       <c r="Z81" s="162" t="n">
-        <v>729.6360871456527</v>
+        <v>729.6360871456524</v>
       </c>
       <c r="AA81" s="162" t="n">
-        <v>782.3311850006577</v>
+        <v>782.3311850006576</v>
       </c>
       <c r="AB81" s="162" t="n">
         <v>833.0508881243018</v>
       </c>
       <c r="AC81" s="163" t="n">
-        <v>879.8825417663353</v>
+        <v>879.882541766335</v>
       </c>
       <c r="AD81" s="164" t="n">
         <v>81341144.08849025</v>
       </c>
       <c r="AE81" s="165" t="n">
-        <v>93153139.89177978</v>
+        <v>93153139.89177975</v>
       </c>
       <c r="AF81" s="165" t="n">
-        <v>105850707.7750005</v>
+        <v>105850707.7750004</v>
       </c>
       <c r="AG81" s="165" t="n">
         <v>121072345.5991296</v>
@@ -8581,7 +8581,7 @@
         <v>1465.925862055849</v>
       </c>
       <c r="H82" s="155" t="n">
-        <v>1207.870021928875</v>
+        <v>1207.870021928876</v>
       </c>
       <c r="I82" s="156" t="n">
         <v>1292.085490181283</v>
@@ -8590,7 +8590,7 @@
         <v>1365.585096171016</v>
       </c>
       <c r="K82" s="156" t="n">
-        <v>1425.325714617606</v>
+        <v>1425.325714617607</v>
       </c>
       <c r="L82" s="157" t="n">
         <v>1465.925862055849</v>
@@ -8605,7 +8605,7 @@
         <v>13723968.6567668</v>
       </c>
       <c r="P82" s="159" t="n">
-        <v>15821532.12846238</v>
+        <v>15821532.12846239</v>
       </c>
       <c r="Q82" s="160" t="n">
         <v>18365857.85980269</v>
@@ -8628,7 +8628,7 @@
         <v>1734.43228783535</v>
       </c>
       <c r="X82" s="157" t="n">
-        <v>1783.837280592851</v>
+        <v>1783.837280592852</v>
       </c>
       <c r="Y82" s="155" t="n">
         <v>1469.345970859544</v>
@@ -8643,7 +8643,7 @@
         <v>1734.43228783535</v>
       </c>
       <c r="AC82" s="157" t="n">
-        <v>1783.837280592851</v>
+        <v>1783.837280592852</v>
       </c>
       <c r="AD82" s="158" t="n">
         <v>10414293.58988598</v>
@@ -8655,7 +8655,7 @@
         <v>13723968.6567668</v>
       </c>
       <c r="AG82" s="159" t="n">
-        <v>15821532.12846238</v>
+        <v>15821532.12846239</v>
       </c>
       <c r="AH82" s="160" t="n">
         <v>18365857.85980269</v>
@@ -8671,13 +8671,13 @@
         <v>612.9416729370949</v>
       </c>
       <c r="D83" s="162" t="n">
-        <v>660.1047790438679</v>
+        <v>660.1047790438678</v>
       </c>
       <c r="E83" s="162" t="n">
-        <v>705.6673748994274</v>
+        <v>705.6673748994272</v>
       </c>
       <c r="F83" s="162" t="n">
-        <v>749.2193252843073</v>
+        <v>749.2193252843074</v>
       </c>
       <c r="G83" s="163" t="n">
         <v>788.5089566515919</v>
@@ -8686,16 +8686,16 @@
         <v>607.8485633052849</v>
       </c>
       <c r="I83" s="162" t="n">
-        <v>656.0021121405234</v>
+        <v>656.0021121405232</v>
       </c>
       <c r="J83" s="162" t="n">
-        <v>702.6850873790767</v>
+        <v>702.6850873790765</v>
       </c>
       <c r="K83" s="162" t="n">
-        <v>747.5137715018392</v>
+        <v>747.5137715018395</v>
       </c>
       <c r="L83" s="163" t="n">
-        <v>788.2260158118191</v>
+        <v>788.226015811819</v>
       </c>
       <c r="M83" s="164" t="n">
         <v>91755437.67837623</v>
@@ -8704,10 +8704,10 @@
         <v>105131335.3893796</v>
       </c>
       <c r="O83" s="165" t="n">
-        <v>119574676.4317673</v>
+        <v>119574676.4317672</v>
       </c>
       <c r="P83" s="165" t="n">
-        <v>136893877.727592</v>
+        <v>136893877.7275921</v>
       </c>
       <c r="Q83" s="166" t="n">
         <v>158509206.5502008</v>
@@ -8718,34 +8718,34 @@
         </is>
       </c>
       <c r="T83" s="161" t="n">
-        <v>725.2323887800079</v>
+        <v>725.2323887800078</v>
       </c>
       <c r="U83" s="162" t="n">
-        <v>781.9367272099826</v>
+        <v>781.9367272099825</v>
       </c>
       <c r="V83" s="162" t="n">
-        <v>836.4597251736333</v>
+        <v>836.4597251736332</v>
       </c>
       <c r="W83" s="162" t="n">
-        <v>888.3196543190835</v>
+        <v>888.3196543190836</v>
       </c>
       <c r="X83" s="163" t="n">
-        <v>935.1244553216516</v>
+        <v>935.1244553216513</v>
       </c>
       <c r="Y83" s="161" t="n">
-        <v>719.2200824142487</v>
+        <v>719.2200824142486</v>
       </c>
       <c r="Z83" s="162" t="n">
-        <v>777.0789780515324</v>
+        <v>777.0789780515323</v>
       </c>
       <c r="AA83" s="162" t="n">
-        <v>832.9190364561807</v>
+        <v>832.9190364561806</v>
       </c>
       <c r="AB83" s="162" t="n">
         <v>886.2848878834252</v>
       </c>
       <c r="AC83" s="163" t="n">
-        <v>934.7672909498905</v>
+        <v>934.7672909498901</v>
       </c>
       <c r="AD83" s="164" t="n">
         <v>91755437.67837623</v>
@@ -8754,10 +8754,10 @@
         <v>105131335.3893796</v>
       </c>
       <c r="AF83" s="165" t="n">
-        <v>119574676.4317673</v>
+        <v>119574676.4317672</v>
       </c>
       <c r="AG83" s="165" t="n">
-        <v>136893877.727592</v>
+        <v>136893877.7275921</v>
       </c>
       <c r="AH83" s="166" t="n">
         <v>158509206.5502008</v>
@@ -8770,49 +8770,49 @@
         </is>
       </c>
       <c r="C84" s="155" t="n">
-        <v>7036.394727151741</v>
+        <v>7036.394727151736</v>
       </c>
       <c r="D84" s="156" t="n">
-        <v>7312.518501574925</v>
+        <v>7312.518501574922</v>
       </c>
       <c r="E84" s="156" t="n">
-        <v>7747.254145988882</v>
+        <v>7747.25414598888</v>
       </c>
       <c r="F84" s="156" t="n">
-        <v>7954.575400994801</v>
+        <v>7954.575400994798</v>
       </c>
       <c r="G84" s="157" t="n">
-        <v>8276.723507749737</v>
+        <v>8276.723507749733</v>
       </c>
       <c r="H84" s="155" t="n">
-        <v>7029.829416395053</v>
+        <v>7029.82941639505</v>
       </c>
       <c r="I84" s="156" t="n">
-        <v>7306.380317092007</v>
+        <v>7306.380317092005</v>
       </c>
       <c r="J84" s="156" t="n">
-        <v>7741.305667019601</v>
+        <v>7741.3056670196</v>
       </c>
       <c r="K84" s="156" t="n">
-        <v>7949.174763829446</v>
+        <v>7949.174763829443</v>
       </c>
       <c r="L84" s="157" t="n">
-        <v>8271.766030274404</v>
+        <v>8271.766030274401</v>
       </c>
       <c r="M84" s="158" t="n">
-        <v>65327897.4562111</v>
+        <v>65327897.45621106</v>
       </c>
       <c r="N84" s="159" t="n">
-        <v>76564698.04524426</v>
+        <v>76564698.04524423</v>
       </c>
       <c r="O84" s="159" t="n">
-        <v>90556170.65654339</v>
+        <v>90556170.65654337</v>
       </c>
       <c r="P84" s="159" t="n">
         <v>106558583.5274029</v>
       </c>
       <c r="Q84" s="160" t="n">
-        <v>127360406.7355469</v>
+        <v>127360406.7355468</v>
       </c>
       <c r="S84" s="32" t="inlineStr">
         <is>
@@ -8820,49 +8820,49 @@
         </is>
       </c>
       <c r="T84" s="155" t="n">
-        <v>4512.207364807332</v>
+        <v>4512.20736480733</v>
       </c>
       <c r="U84" s="156" t="n">
-        <v>4689.276414635216</v>
+        <v>4689.276414635215</v>
       </c>
       <c r="V84" s="156" t="n">
-        <v>4968.05801409545</v>
+        <v>4968.058014095449</v>
       </c>
       <c r="W84" s="156" t="n">
-        <v>5101.00628234837</v>
+        <v>5101.006282348369</v>
       </c>
       <c r="X84" s="157" t="n">
-        <v>5307.589215259919</v>
+        <v>5307.589215259916</v>
       </c>
       <c r="Y84" s="155" t="n">
-        <v>4509.074449068287</v>
+        <v>4509.074449068285</v>
       </c>
       <c r="Z84" s="156" t="n">
-        <v>4686.347390508336</v>
+        <v>4686.347390508334</v>
       </c>
       <c r="AA84" s="156" t="n">
-        <v>4965.219565847233</v>
+        <v>4965.219565847232</v>
       </c>
       <c r="AB84" s="156" t="n">
-        <v>5098.429307585334</v>
+        <v>5098.429307585331</v>
       </c>
       <c r="AC84" s="157" t="n">
-        <v>5305.223747568379</v>
+        <v>5305.223747568377</v>
       </c>
       <c r="AD84" s="158" t="n">
-        <v>65327897.4562111</v>
+        <v>65327897.45621106</v>
       </c>
       <c r="AE84" s="159" t="n">
-        <v>76564698.04524426</v>
+        <v>76564698.04524423</v>
       </c>
       <c r="AF84" s="159" t="n">
-        <v>90556170.65654339</v>
+        <v>90556170.65654337</v>
       </c>
       <c r="AG84" s="159" t="n">
         <v>106558583.5274029</v>
       </c>
       <c r="AH84" s="160" t="n">
-        <v>127360406.7355469</v>
+        <v>127360406.7355468</v>
       </c>
     </row>
     <row r="85" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -8872,7 +8872,7 @@
         </is>
       </c>
       <c r="C85" s="179" t="n">
-        <v>988.0627323636138</v>
+        <v>988.0627323636136</v>
       </c>
       <c r="D85" s="180" t="n">
         <v>1070.46901103065</v>
@@ -8887,13 +8887,13 @@
         <v>1320.952317649107</v>
       </c>
       <c r="H85" s="179" t="n">
-        <v>980.2752935322545</v>
+        <v>980.2752935322542</v>
       </c>
       <c r="I85" s="180" t="n">
         <v>1064.169046593379</v>
       </c>
       <c r="J85" s="180" t="n">
-        <v>1155.415665668235</v>
+        <v>1155.415665668234</v>
       </c>
       <c r="K85" s="180" t="n">
         <v>1238.709096626751</v>
@@ -8908,13 +8908,13 @@
         <v>181696033.4346238</v>
       </c>
       <c r="O85" s="183" t="n">
-        <v>210130847.0883107</v>
+        <v>210130847.0883106</v>
       </c>
       <c r="P85" s="183" t="n">
         <v>243452461.2549949</v>
       </c>
       <c r="Q85" s="184" t="n">
-        <v>285869613.2857477</v>
+        <v>285869613.2857476</v>
       </c>
       <c r="S85" s="51" t="inlineStr">
         <is>
@@ -8928,10 +8928,10 @@
         <v>1205.060331151552</v>
       </c>
       <c r="V85" s="186" t="n">
-        <v>1303.69507527979</v>
+        <v>1303.695075279789</v>
       </c>
       <c r="W85" s="186" t="n">
-        <v>1391.204482554559</v>
+        <v>1391.204482554558</v>
       </c>
       <c r="X85" s="187" t="n">
         <v>1477.347792803904</v>
@@ -8949,7 +8949,7 @@
         <v>1388.313858028959</v>
       </c>
       <c r="AC85" s="187" t="n">
-        <v>1476.771853100728</v>
+        <v>1476.771853100727</v>
       </c>
       <c r="AD85" s="188" t="n">
         <v>157083335.1345873</v>
@@ -8958,13 +8958,13 @@
         <v>181696033.4346238</v>
       </c>
       <c r="AF85" s="189" t="n">
-        <v>210130847.0883107</v>
+        <v>210130847.0883106</v>
       </c>
       <c r="AG85" s="189" t="n">
         <v>243452461.2549949</v>
       </c>
       <c r="AH85" s="190" t="n">
-        <v>285869613.2857477</v>
+        <v>285869613.2857476</v>
       </c>
     </row>
     <row r="86" ht="15" customHeight="1" thickBot="1"/>
@@ -9287,7 +9287,7 @@
         <v>123534.7071570992</v>
       </c>
       <c r="E90" s="75" t="n">
-        <v>131781.8177623025</v>
+        <v>131781.8177623026</v>
       </c>
       <c r="F90" s="75" t="n">
         <v>142072.9871695138</v>
@@ -9331,7 +9331,7 @@
         </is>
       </c>
       <c r="T90" s="74" t="n">
-        <v>94022.74165982254</v>
+        <v>94022.74165982255</v>
       </c>
       <c r="U90" s="75" t="n">
         <v>100671.4901834258</v>
@@ -9361,7 +9361,7 @@
         <v>30.16412813999912</v>
       </c>
       <c r="AD90" s="74" t="n">
-        <v>94816.92580116398</v>
+        <v>94816.92580116399</v>
       </c>
       <c r="AE90" s="75" t="n">
         <v>101302.3963567819</v>
@@ -9440,7 +9440,7 @@
         <v>26672.47541003757</v>
       </c>
       <c r="O91" s="80" t="n">
-        <v>27770.34595583852</v>
+        <v>27770.34595583853</v>
       </c>
       <c r="P91" s="80" t="n">
         <v>29635.90281643001</v>
@@ -9460,7 +9460,7 @@
         <v>26179.60736526955</v>
       </c>
       <c r="V91" s="80" t="n">
-        <v>27309.07140925933</v>
+        <v>27309.07140925934</v>
       </c>
       <c r="W91" s="80" t="n">
         <v>29203.48223836126</v>
@@ -9490,7 +9490,7 @@
         <v>26368.28980156898</v>
       </c>
       <c r="AF91" s="80" t="n">
-        <v>27453.21801292077</v>
+        <v>27453.21801292078</v>
       </c>
       <c r="AG91" s="80" t="n">
         <v>29296.98444180949</v>
@@ -9530,7 +9530,7 @@
         <v>150017.8513952683</v>
       </c>
       <c r="E92" s="86" t="n">
-        <v>159407.5215038081</v>
+        <v>159407.5215038082</v>
       </c>
       <c r="F92" s="86" t="n">
         <v>171615.0662994452</v>
@@ -9560,7 +9560,7 @@
         <v>150990.2302680237</v>
       </c>
       <c r="O92" s="86" t="n">
-        <v>160118.3466929539</v>
+        <v>160118.346692954</v>
       </c>
       <c r="P92" s="86" t="n">
         <v>172031.9561052827</v>
@@ -9795,7 +9795,7 @@
         <v>170168.2283848731</v>
       </c>
       <c r="P94" s="86" t="n">
-        <v>183132.2484568503</v>
+        <v>183132.2484568502</v>
       </c>
       <c r="Q94" s="87" t="n">
         <v>201096.1366035948</v>
@@ -9815,16 +9815,16 @@
         <v>142953.2980884953</v>
       </c>
       <c r="W94" s="86" t="n">
-        <v>154104.2991247606</v>
+        <v>154104.2991247607</v>
       </c>
       <c r="X94" s="87" t="n">
-        <v>169506.0006699097</v>
+        <v>169506.0006699098</v>
       </c>
       <c r="Y94" s="85" t="n">
         <v>1057.63037909861</v>
       </c>
       <c r="Z94" s="86" t="n">
-        <v>840.4860188768221</v>
+        <v>840.486018876822</v>
       </c>
       <c r="AA94" s="86" t="n">
         <v>607.685870427589</v>
@@ -9848,7 +9848,7 @@
         <v>154458.0976152196</v>
       </c>
       <c r="AH94" s="87" t="n">
-        <v>169570.7670613155</v>
+        <v>169570.7670613156</v>
       </c>
       <c r="AJ94" s="126" t="n">
         <v>37.51602533606992</v>
@@ -9994,7 +9994,7 @@
         <v>169734.9774373071</v>
       </c>
       <c r="E96" s="133" t="n">
-        <v>181137.8729381732</v>
+        <v>181137.8729381733</v>
       </c>
       <c r="F96" s="133" t="n">
         <v>196111.2444344421</v>
@@ -10012,7 +10012,7 @@
         <v>728.145787461238</v>
       </c>
       <c r="K96" s="133" t="n">
-        <v>425.9909164274645</v>
+        <v>425.9909164274644</v>
       </c>
       <c r="L96" s="134" t="n">
         <v>81.38165439183648</v>
@@ -10024,7 +10024,7 @@
         <v>170739.8218509265</v>
       </c>
       <c r="O96" s="133" t="n">
-        <v>181866.0187256345</v>
+        <v>181866.0187256346</v>
       </c>
       <c r="P96" s="133" t="n">
         <v>196537.2353508696</v>
@@ -10056,7 +10056,7 @@
         <v>1067.689752732331</v>
       </c>
       <c r="Z96" s="136" t="n">
-        <v>850.690976620897</v>
+        <v>850.6909766208969</v>
       </c>
       <c r="AA96" s="136" t="n">
         <v>618.1060190396307</v>
@@ -10080,7 +10080,7 @@
         <v>175358.3743668982</v>
       </c>
       <c r="AH96" s="137" t="n">
-        <v>193577.3712679565</v>
+        <v>193577.3712679566</v>
       </c>
       <c r="AJ96" s="138" t="n"/>
       <c r="AK96" s="139" t="n"/>
